--- a/results/job_matches_2026-07-28.xlsx
+++ b/results/job_matches_2026-07-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Solutions Architect (Cloud Transformation)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OrangePeople</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.3</v>
+        <v>23.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a7e6b8f9c661779</t>
+          <t>https://www.indeed.com/viewjob?jk=d09b36193d9c21c6</t>
         </is>
       </c>
     </row>
@@ -508,20 +508,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.6</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09b36193d9c21c6</t>
+          <t>https://www.indeed.com/viewjob?jk=20e8b241f5073b73</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e8b241f5073b73</t>
+          <t>https://www.indeed.com/viewjob?jk=9a43d246f182c799</t>
         </is>
       </c>
     </row>
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a43d246f182c799</t>
+          <t>https://www.indeed.com/viewjob?jk=75897b83126c3579</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75897b83126c3579</t>
+          <t>https://www.indeed.com/viewjob?jk=4e92864ad72da7b0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, RDS, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e92864ad72da7b0</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e71e87e20fcad6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer- Veterans Affairs</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>THUNDERYARD SOLUTIONS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, RDS, Google Cloud Platform, GCP</t>
+          <t>Kinesis, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Cloud Storage</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e71e87e20fcad6</t>
+          <t>https://www.indeed.com/viewjob?jk=7b91074aae697c25</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer- Veterans Affairs</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>THUNDERYARD SOLUTIONS</t>
+          <t>Magpie Health Analytics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Cloud Storage</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SNS, RDS, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b91074aae697c25</t>
+          <t>https://www.indeed.com/viewjob?jk=81821640f49f76e3</t>
         </is>
       </c>
     </row>
@@ -818,25 +818,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Business Intelligence Data Modeler Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f88f3978f6e2de83</t>
+          <t>https://www.indeed.com/viewjob?jk=29badf7873509f1c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BI Data Engineer II</t>
+          <t>AWS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Boston Beer Company</t>
+          <t>Empower AI Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62785c4010471f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=34befeada094f827</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Enterprise Information Architect I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>L.L. Bean, Inc.</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Freeport, ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ECS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd6d7b7a1225dcc2</t>
+          <t>https://www.indeed.com/viewjob?jk=5e3771f0c36b6f26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51edf63fd9ce4d7a</t>
+          <t>https://www.indeed.com/viewjob?jk=f88f3978f6e2de83</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>BI Data Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>The Boston Beer Company</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd136a2c45725af</t>
+          <t>https://www.indeed.com/viewjob?jk=62785c4010471f7c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Spark / Databricks Platform Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e214057fae5adc71</t>
+          <t>https://www.indeed.com/viewjob?jk=a40f6ae7d2456a50</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - AI</t>
+          <t>Enterprise Information Architect I</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lowe's Home Improvement</t>
+          <t>L.L. Bean, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Freeport, ME, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
+          <t>ECS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1942c35e56392e</t>
+          <t>https://www.indeed.com/viewjob?jk=cd6d7b7a1225dcc2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer - AI</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lowe's Home Improvement</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b404e83cdfac818</t>
+          <t>https://www.indeed.com/viewjob?jk=51edf63fd9ce4d7a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Arkansas City, KS, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Oracle, PostgreSQL, MySQL, Cassandra</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=511a0ee05b471605</t>
+          <t>https://www.indeed.com/viewjob?jk=acd136a2c45725af</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Spark / Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, MongoDB</t>
+          <t>RDS, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad2d81d6d9a2d31</t>
+          <t>https://www.indeed.com/viewjob?jk=e214057fae5adc71</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer (With TS/SCI Clearance and a current Full Scope Poly)</t>
+          <t>Sr Software Engineer - AI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>J&amp;T Business Consulting</t>
+          <t>Lowe's Home Improvement</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fea98a47c7da3e79</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1942c35e56392e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Developer 3 (Full Stack Developer)</t>
+          <t>Software Engineer - AI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Edgewater Technical Associates</t>
+          <t>Lowe's Home Improvement</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Los Alamos, NM, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e39c95265674fb</t>
+          <t>https://www.indeed.com/viewjob?jk=4b404e83cdfac818</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Arkansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Oracle, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c0930580a5bcd07</t>
+          <t>https://www.indeed.com/viewjob?jk=511a0ee05b471605</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Avantos AI</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, MongoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728e979a13366d12</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad2d81d6d9a2d31</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irving, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, RDS, Scala, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b818545ba973b739</t>
+          <t>https://www.indeed.com/viewjob?jk=f4591ff172a960b9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Developer – Full Stack (Java Spring Boot, React, PostgreSQL)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1353,15 +1353,15 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, ECS, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73033b8f87058bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=38439f74465262d5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Security Automation &amp; SOAR Engineer</t>
+          <t>Senior Data Science Engineer (With TS/SCI Clearance and a current Full Scope Poly)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>J&amp;T Business Consulting</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=945bfa278c31dac2</t>
+          <t>https://www.indeed.com/viewjob?jk=fea98a47c7da3e79</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>East Penn Manufacturing</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e660e8c44066de</t>
+          <t>https://www.indeed.com/viewjob?jk=1c0930580a5bcd07</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Software Developer 3 (Full Stack Developer)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>East Penn Manufacturing</t>
+          <t>Edgewater Technical Associates</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Los Alamos, NM, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=def777e7298305bd</t>
+          <t>https://www.indeed.com/viewjob?jk=64e39c95265674fb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud Developer</t>
+          <t>Senior Data Specialist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kansara systems</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, ETL, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0ebce6f320f9837</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f0a26367981106</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>Avantos AI</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd62b8e1edffefb2</t>
+          <t>https://www.indeed.com/viewjob?jk=728e979a13366d12</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Irving, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73c49ea64a65e4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=b818545ba973b739</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - GCP</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>East Penn Manufacturing</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8432eda41e25a208</t>
+          <t>https://www.indeed.com/viewjob?jk=75e660e8c44066de</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>East Penn Manufacturing</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff16008b78c40ca</t>
+          <t>https://www.indeed.com/viewjob?jk=def777e7298305bd</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c3f08d70fed55ec</t>
+          <t>https://www.indeed.com/viewjob?jk=73033b8f87058bf3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - GCP</t>
+          <t>Cloud Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Kansara systems</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, ETL, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad10bcc1b9c0d99</t>
+          <t>https://www.indeed.com/viewjob?jk=b0ebce6f320f9837</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer – 1099 Contract</t>
+          <t>Software Engineer, Reconciliation &amp; Reporting</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bitcot Technologies Pvt Ltd</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56400bd32a7b810d</t>
+          <t>https://www.indeed.com/viewjob?jk=9c826fbf927fd818</t>
         </is>
       </c>
     </row>
@@ -1768,12 +1768,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c29f94189cd7da4</t>
+          <t>https://www.indeed.com/viewjob?jk=fd62b8e1edffefb2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Developer 3 – Contract Position</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BranCore Technologies</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e60ccdf9474927</t>
+          <t>https://www.indeed.com/viewjob?jk=73c49ea64a65e4e4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Azure Cloud Developer</t>
+          <t>Associate Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f040e735595615</t>
+          <t>https://www.indeed.com/viewjob?jk=8432eda41e25a208</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>OrangePeople</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4c6abe99182f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff16008b78c40ca</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Chargie</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da930629a1994ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=2c3f08d70fed55ec</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Associate Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab876d2e4fa9584b</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad10bcc1b9c0d99</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>AI DevOps Engineer – 1099 Contract</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>Bitcot Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,19 +2001,19 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b99b879200d82b7</t>
+          <t>https://www.indeed.com/viewjob?jk=56400bd32a7b810d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lucet</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2022,11 +2022,11 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c66caa75fc25ec21</t>
+          <t>https://www.indeed.com/viewjob?jk=2c29f94189cd7da4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>OrangePeople</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d507f97d89d506</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4c6abe99182f2f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed Software Engineer (FDE)</t>
+          <t>Senior Data &amp; Backend Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Chargie</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d38e42153f6fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=da930629a1994ea8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Software Engineer IV</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Innovative Tech Solutions</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Spark, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77b5643dbfd08cb8</t>
+          <t>https://www.indeed.com/viewjob?jk=ab876d2e4fa9584b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hive, Spark, PySpark, Scala, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2a0a88a6bb4e38</t>
+          <t>https://www.indeed.com/viewjob?jk=8b99b879200d82b7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Region 4 Education Service Center</t>
+          <t>Lucet</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f972668b159bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=c66caa75fc25ec21</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Doggett Equipment Services Group</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663cb751d821c5e4</t>
+          <t>https://www.indeed.com/viewjob?jk=74d507f97d89d506</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hive, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c5869f8a07d44cc</t>
+          <t>https://www.indeed.com/viewjob?jk=dc2a0a88a6bb4e38</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Jazwares</t>
+          <t>Purple Wave Auction</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7985331f140b0ede</t>
+          <t>https://www.indeed.com/viewjob?jk=f455b3604d919def</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Western Union</t>
+          <t>Region 4 Education Service Center</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d469e2c445c6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=8f972668b159bfe1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS, Enterprise IAM</t>
+          <t>Encryption‑as‑a‑Service (EaaS) Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eac59fd94e904980</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd6c484ead70174</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Doggett Equipment Services Group</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2cf1215aaca8c2</t>
+          <t>https://www.indeed.com/viewjob?jk=663cb751d821c5e4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Python Senior Developer - Data Analysis, SQL</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,19 +2456,19 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630de2ec3682e100</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2cf1215aaca8c2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cloud Engineer — multi-cloud (AWS &amp; Azure), infrastructure &amp; data services</t>
+          <t>Python Senior Developer - Data Analysis, SQL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NeevSys</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d9834a85f42798</t>
+          <t>https://www.indeed.com/viewjob?jk=630de2ec3682e100</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. IT Analyst</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tebra</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Corona del Mar, CA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ELT, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, ETL, ELT, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55760e04a88682c7</t>
+          <t>https://www.indeed.com/viewjob?jk=dfb5747a9d41a47e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer 2- Kiewit Technology Group</t>
+          <t>Cloud Engineer — multi-cloud (AWS &amp; Azure), infrastructure &amp; data services</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>NeevSys</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e16ff09aa0b39352</t>
+          <t>https://www.indeed.com/viewjob?jk=61d9834a85f42798</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MGIC</t>
+          <t>Tebra</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>Corona del Mar, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40c5bedf068bb80</t>
+          <t>https://www.indeed.com/viewjob?jk=55760e04a88682c7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 2- Kiewit Technology Group</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TRIPLECOM</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>North Brunswick, NJ, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e6b5d69c186e13</t>
+          <t>https://www.indeed.com/viewjob?jk=e16ff09aa0b39352</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Embedded Product Analytics Senior Engineer</t>
+          <t>Senior Systems Engineer Analyst</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>MGIC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Mossville, IL, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01a1b2e1bcd66d65</t>
+          <t>https://www.indeed.com/viewjob?jk=c40c5bedf068bb80</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AWS Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Arkatechture</t>
+          <t>TRIPLECOM</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>North Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3391e6126aa7cb2b</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e6b5d69c186e13</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Principle Data &amp; IT Platform Engineer</t>
+          <t>Embedded Product Analytics Senior Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>OxyChem</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Mossville, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, NoSQL, Power BI, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aafa6193d63da13a</t>
+          <t>https://www.indeed.com/viewjob?jk=01a1b2e1bcd66d65</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full Stack Developer -Angular, Typescript, Bedrock</t>
+          <t>AWS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Arkatechture</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Malvern, AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=729151ced6fff1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=3391e6126aa7cb2b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Nelnet</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
+          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44964b0a055385de</t>
+          <t>https://www.indeed.com/viewjob?jk=502f8e4e0f72f9d7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Public Sector (Defense Industrial Base)</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87283036c68270bc</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0b92db58bd05b8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services (Banking and Payments)</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3e39e9feb6cbc6</t>
+          <t>https://www.indeed.com/viewjob?jk=b6cd8290f0bbfe00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Salesforce Development Engineer III</t>
+          <t>Principle Data &amp; IT Platform Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>OxyChem</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, NoSQL, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4b298a9510a69c</t>
+          <t>https://www.indeed.com/viewjob?jk=aafa6193d63da13a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Development Engineer – Python</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cyient</t>
+          <t>Nelnet</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Champaign, IL, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dc8bc961812dc0</t>
+          <t>https://www.indeed.com/viewjob?jk=44964b0a055385de</t>
         </is>
       </c>
     </row>
@@ -3023,17 +3023,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Machine Learning Engineer (NLP/LLM Focus)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Argonne National Laboratory</t>
+          <t>Call Box</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Lemont, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Spark, Scala, ETL, MLOps, MLflow, Terraform, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1699fa0e2d2c879d</t>
+          <t>https://www.indeed.com/viewjob?jk=6fea9b3e6393fbcc</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Public Trust Clearance Required</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Core-CSI LLC</t>
+          <t>Argonne National Laboratory</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Lemont, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Polars, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df52133313b370b6</t>
+          <t>https://www.indeed.com/viewjob?jk=1699fa0e2d2c879d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Senior Data Engineer - Public Trust Clearance Required</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Core-CSI LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Polars, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4852036d2a4d2871</t>
+          <t>https://www.indeed.com/viewjob?jk=df52133313b370b6</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III-ETL/PySpark</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf6ee00929d1c54</t>
+          <t>https://www.indeed.com/viewjob?jk=4852036d2a4d2871</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e729f2a707e926b3</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf6ee00929d1c54</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
+          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744d47dbc385f247</t>
+          <t>https://www.indeed.com/viewjob?jk=e729f2a707e926b3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Northwestern Medicine</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Microsoft SSIS, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c90f2bb9aa42025</t>
+          <t>https://www.indeed.com/viewjob?jk=744d47dbc385f247</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Python Solutions Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Northwestern Medicine</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Microsoft SSIS, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a1e114754b6273</t>
+          <t>https://www.indeed.com/viewjob?jk=2c90f2bb9aa42025</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Intermediate or Sr Software Developer (AI Platform &amp; Applications)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=795435ece1bb17ca</t>
+          <t>https://www.indeed.com/viewjob?jk=d1783e76eef53a01</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Python Solutions Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Kubernetes, SonarQube, Git</t>
+          <t>AWS, Glue, S3, RDS, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e01c370f5d19ca30</t>
+          <t>https://www.indeed.com/viewjob?jk=c4a1e114754b6273</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Azure Integration Architect</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>intent design ltd</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, NoSQL, Azure DevOps, Terraform, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7a2db86bb37412</t>
+          <t>https://www.indeed.com/viewjob?jk=795435ece1bb17ca</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Azure Integration Architect</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Intent Design Pvt Ltd</t>
+          <t>The Akanksha LLC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, NoSQL, Azure DevOps, Terraform, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=396b021d33329d73</t>
+          <t>https://www.indeed.com/viewjob?jk=67197d81925e64b6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Infrastructure Architect</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>PLACE Corporate Careers</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3470,321 +3470,6 @@
         </is>
       </c>
       <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cf7b53a97b9f39a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Cloud Data Architect</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2842f8dbc1705e3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Cloud Architect (Azure)</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Phoenix Business Consulting</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0b3a86d91498e0d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>DevOps Architect</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Phoenix Business Consulting</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=176b1dbed7f93f82</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Junior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>MetLife</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Bridgewater, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1155785404399fad</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Blue Yonder</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afa14c95807983ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Blue Yonder</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Scottsdale, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, GitHub Actions, Docker, Kubernetes, AKS, SonarQube</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=52e66699cb75c9e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior Data Architect</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>The Akanksha LLC</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=67197d81925e64b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Packaged/SaaS Application Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57e0eee7c9431a4b</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>PLACE Corporate Careers</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>OR, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=94d6622d48d77919</t>
         </is>

--- a/results/job_matches_2026-07-28.xlsx
+++ b/results/job_matches_2026-07-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solutions Architect (Cloud Transformation)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>OrangePeople</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.6</v>
+        <v>24.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09b36193d9c21c6</t>
+          <t>https://www.indeed.com/viewjob?jk=1a7e6b8f9c661779</t>
         </is>
       </c>
     </row>
@@ -508,20 +508,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>23.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e8b241f5073b73</t>
+          <t>https://www.indeed.com/viewjob?jk=d09b36193d9c21c6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a43d246f182c799</t>
+          <t>https://www.indeed.com/viewjob?jk=20e8b241f5073b73</t>
         </is>
       </c>
     </row>
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75897b83126c3579</t>
+          <t>https://www.indeed.com/viewjob?jk=9a43d246f182c799</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e92864ad72da7b0</t>
+          <t>https://www.indeed.com/viewjob?jk=75897b83126c3579</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, RDS, Google Cloud Platform, GCP</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e71e87e20fcad6</t>
+          <t>https://www.indeed.com/viewjob?jk=4e92864ad72da7b0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer- Veterans Affairs</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>THUNDERYARD SOLUTIONS</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Cloud Storage</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, RDS, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b91074aae697c25</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e71e87e20fcad6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer- Veterans Affairs</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Magpie Health Analytics</t>
+          <t>THUNDERYARD SOLUTIONS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -731,77 +731,77 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SNS, RDS, Hadoop, Spark, PySpark</t>
+          <t>Kinesis, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Cloud Storage</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81821640f49f76e3</t>
+          <t>https://www.indeed.com/viewjob?jk=7b91074aae697c25</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Magpie Health Analytics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SNS, RDS, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84fb98656d187561</t>
+          <t>https://www.indeed.com/viewjob?jk=81821640f49f76e3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3d05891aeb413c</t>
+          <t>https://www.indeed.com/viewjob?jk=84fb98656d187561</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Modeler Engineer II</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29badf7873509f1c</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3d05891aeb413c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AWS Cloud Infrastructure Engineer</t>
+          <t>Business Intelligence Data Modeler Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Empower AI Inc.</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34befeada094f827</t>
+          <t>https://www.indeed.com/viewjob?jk=29badf7873509f1c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Empower AI Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e3771f0c36b6f26</t>
+          <t>https://www.indeed.com/viewjob?jk=34befeada094f827</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f88f3978f6e2de83</t>
+          <t>https://www.indeed.com/viewjob?jk=5e3771f0c36b6f26</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BI Data Engineer II</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Boston Beer Company</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62785c4010471f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=f88f3978f6e2de83</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>BI Data Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>The Boston Beer Company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40f6ae7d2456a50</t>
+          <t>https://www.indeed.com/viewjob?jk=62785c4010471f7c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Enterprise Information Architect I</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>L.L. Bean, Inc.</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Freeport, ME, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ECS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd6d7b7a1225dcc2</t>
+          <t>https://www.indeed.com/viewjob?jk=a40f6ae7d2456a50</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Enterprise Information Architect I</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>L.L. Bean, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Freeport, ME, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>ECS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51edf63fd9ce4d7a</t>
+          <t>https://www.indeed.com/viewjob?jk=cd6d7b7a1225dcc2</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd136a2c45725af</t>
+          <t>https://www.indeed.com/viewjob?jk=51edf63fd9ce4d7a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Spark / Databricks Platform Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e214057fae5adc71</t>
+          <t>https://www.indeed.com/viewjob?jk=acd136a2c45725af</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - AI</t>
+          <t>Spark / Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lowe's Home Improvement</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
+          <t>RDS, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1942c35e56392e</t>
+          <t>https://www.indeed.com/viewjob?jk=e214057fae5adc71</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer - AI</t>
+          <t>Sr Software Engineer - AI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b404e83cdfac818</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1942c35e56392e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - AI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Lowe's Home Improvement</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Arkansas City, KS, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Oracle, PostgreSQL, MySQL, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=511a0ee05b471605</t>
+          <t>https://www.indeed.com/viewjob?jk=4b404e83cdfac818</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer (With TS/SCI Clearance and a current Full Scope Poly)</t>
+          <t>Software Developer 3 (Full Stack Developer)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>J&amp;T Business Consulting</t>
+          <t>Edgewater Technical Associates</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Los Alamos, NM, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fea98a47c7da3e79</t>
+          <t>https://www.indeed.com/viewjob?jk=64e39c95265674fb</t>
         </is>
       </c>
     </row>
@@ -1448,25 +1448,25 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Developer 3 (Full Stack Developer)</t>
+          <t>Senior Data Specialist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Edgewater Technical Associates</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Los Alamos, NM, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e39c95265674fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f0a26367981106</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Specialist</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Avantos AI</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f0a26367981106</t>
+          <t>https://www.indeed.com/viewjob?jk=728e979a13366d12</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Avantos AI</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728e979a13366d12</t>
+          <t>https://www.indeed.com/viewjob?jk=b818545ba973b739</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irving, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b818545ba973b739</t>
+          <t>https://www.indeed.com/viewjob?jk=73033b8f87058bf3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Senior Security Automation &amp; SOAR Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>East Penn Manufacturing</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e660e8c44066de</t>
+          <t>https://www.indeed.com/viewjob?jk=945bfa278c31dac2</t>
         </is>
       </c>
     </row>
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=def777e7298305bd</t>
+          <t>https://www.indeed.com/viewjob?jk=75e660e8c44066de</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>East Penn Manufacturing</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73033b8f87058bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=def777e7298305bd</t>
         </is>
       </c>
     </row>
@@ -1728,25 +1728,25 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer, Reconciliation &amp; Reporting</t>
+          <t>Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Symple Lending</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, SQS, SNS, API Gateway, Scala, Kafka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c826fbf927fd818</t>
+          <t>https://www.indeed.com/viewjob?jk=f3dca5d46f438997</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Big Data / AWS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd62b8e1edffefb2</t>
+          <t>https://www.indeed.com/viewjob?jk=8515f265503b068a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Reconciliation &amp; Reporting</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73c49ea64a65e4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=9c826fbf927fd818</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - GCP</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8432eda41e25a208</t>
+          <t>https://www.indeed.com/viewjob?jk=fd62b8e1edffefb2</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff16008b78c40ca</t>
+          <t>https://www.indeed.com/viewjob?jk=73c49ea64a65e4e4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c3f08d70fed55ec</t>
+          <t>https://www.indeed.com/viewjob?jk=8432eda41e25a208</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - GCP</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad10bcc1b9c0d99</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff16008b78c40ca</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer – 1099 Contract</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bitcot Technologies Pvt Ltd</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56400bd32a7b810d</t>
+          <t>https://www.indeed.com/viewjob?jk=2c3f08d70fed55ec</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c29f94189cd7da4</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad10bcc1b9c0d99</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI DevOps Engineer – 1099 Contract</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OrangePeople</t>
+          <t>Bitcot Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4c6abe99182f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=56400bd32a7b810d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Chargie</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da930629a1994ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=2c29f94189cd7da4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>OrangePeople</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab876d2e4fa9584b</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4c6abe99182f2f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Senior Data &amp; Backend Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>Chargie</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b99b879200d82b7</t>
+          <t>https://www.indeed.com/viewjob?jk=da930629a1994ea8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Software Engineer IV</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Lucet</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Spark, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c66caa75fc25ec21</t>
+          <t>https://www.indeed.com/viewjob?jk=ab876d2e4fa9584b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d507f97d89d506</t>
+          <t>https://www.indeed.com/viewjob?jk=8b99b879200d82b7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>Lucet</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hive, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,19 +2281,19 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2a0a88a6bb4e38</t>
+          <t>https://www.indeed.com/viewjob?jk=c66caa75fc25ec21</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Purple Wave Auction</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2302,11 +2302,11 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f455b3604d919def</t>
+          <t>https://www.indeed.com/viewjob?jk=74d507f97d89d506</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Forward Deployed Software Engineer (FDE)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Region 4 Education Service Center</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f972668b159bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d38e42153f6fb0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Encryption‑as‑a‑Service (EaaS) Platform Engineer</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Innovative Tech Solutions</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd6c484ead70174</t>
+          <t>https://www.indeed.com/viewjob?jk=77b5643dbfd08cb8</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Doggett Equipment Services Group</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hive, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663cb751d821c5e4</t>
+          <t>https://www.indeed.com/viewjob?jk=dc2a0a88a6bb4e38</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,42 +2446,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2cf1215aaca8c2</t>
+          <t>https://www.indeed.com/viewjob?jk=93f7c2338fe900a7</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Python Senior Developer - Data Analysis, SQL</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Purple Wave Auction</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630de2ec3682e100</t>
+          <t>https://www.indeed.com/viewjob?jk=f455b3604d919def</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. IT Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>Region 4 Education Service Center</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, ETL, ELT, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfb5747a9d41a47e</t>
+          <t>https://www.indeed.com/viewjob?jk=8f972668b159bfe1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Engineer — multi-cloud (AWS &amp; Azure), infrastructure &amp; data services</t>
+          <t>Encryption‑as‑a‑Service (EaaS) Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NeevSys</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d9834a85f42798</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd6c484ead70174</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tebra</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Corona del Mar, CA, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ELT, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55760e04a88682c7</t>
+          <t>https://www.indeed.com/viewjob?jk=ac2139dad458ba99</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer 2- Kiewit Technology Group</t>
+          <t>Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Doggett Equipment Services Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e16ff09aa0b39352</t>
+          <t>https://www.indeed.com/viewjob?jk=663cb751d821c5e4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer Analyst</t>
+          <t>Software Engineering SMTS, Enterprise IAM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MGIC</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40c5bedf068bb80</t>
+          <t>https://www.indeed.com/viewjob?jk=eac59fd94e904980</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TRIPLECOM</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>North Brunswick, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e6b5d69c186e13</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2cf1215aaca8c2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Embedded Product Analytics Senior Engineer</t>
+          <t>Python Senior Developer - Data Analysis, SQL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Mossville, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01a1b2e1bcd66d65</t>
+          <t>https://www.indeed.com/viewjob?jk=630de2ec3682e100</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AWS Cloud Infrastructure Engineer</t>
+          <t>Sr. IT Analyst</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Arkatechture</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, ETL, ELT, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3391e6126aa7cb2b</t>
+          <t>https://www.indeed.com/viewjob?jk=dfb5747a9d41a47e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>Cloud Engineer — multi-cloud (AWS &amp; Azure), infrastructure &amp; data services</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>NeevSys</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=502f8e4e0f72f9d7</t>
+          <t>https://www.indeed.com/viewjob?jk=61d9834a85f42798</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Tebra</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Corona del Mar, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0b92db58bd05b8</t>
+          <t>https://www.indeed.com/viewjob?jk=55760e04a88682c7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>Software Engineer 2- Kiewit Technology Group</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6cd8290f0bbfe00</t>
+          <t>https://www.indeed.com/viewjob?jk=e16ff09aa0b39352</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Principle Data &amp; IT Platform Engineer</t>
+          <t>Senior Systems Engineer Analyst</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>OxyChem</t>
+          <t>MGIC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, NoSQL, Power BI, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aafa6193d63da13a</t>
+          <t>https://www.indeed.com/viewjob?jk=c40c5bedf068bb80</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Nelnet</t>
+          <t>TRIPLECOM</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>North Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44964b0a055385de</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e6b5d69c186e13</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Embedded Product Analytics Senior Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Pensacola, FL, US USA</t>
+          <t>Mossville, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, AKS</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d13a1873aa87c8</t>
+          <t>https://www.indeed.com/viewjob?jk=01a1b2e1bcd66d65</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>Arkatechture</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb73b1bf6741a5f3</t>
+          <t>https://www.indeed.com/viewjob?jk=3391e6126aa7cb2b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (NLP/LLM Focus)</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Call Box</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, ETL, MLOps, MLflow, Terraform, Docker</t>
+          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fea9b3e6393fbcc</t>
+          <t>https://www.indeed.com/viewjob?jk=502f8e4e0f72f9d7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Argonne National Laboratory</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Lemont, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1699fa0e2d2c879d</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0b92db58bd05b8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Public Trust Clearance Required</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Core-CSI LLC</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Polars, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df52133313b370b6</t>
+          <t>https://www.indeed.com/viewjob?jk=b6cd8290f0bbfe00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Full Stack Developer -Angular, Typescript, Bedrock</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Malvern, AR, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4852036d2a4d2871</t>
+          <t>https://www.indeed.com/viewjob?jk=729151ced6fff1a5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Nelnet</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf6ee00929d1c54</t>
+          <t>https://www.indeed.com/viewjob?jk=44964b0a055385de</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Principle Data &amp; IT Platform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>OxyChem</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, NoSQL, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e729f2a707e926b3</t>
+          <t>https://www.indeed.com/viewjob?jk=aafa6193d63da13a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Development Engineer – Python</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Cyient</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Champaign, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744d47dbc385f247</t>
+          <t>https://www.indeed.com/viewjob?jk=12dc8bc961812dc0</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Salesforce Development Engineer III</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Northwestern Medicine</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Microsoft SSIS, Git</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c90f2bb9aa42025</t>
+          <t>https://www.indeed.com/viewjob?jk=8e4b298a9510a69c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Intermediate or Sr Software Developer (AI Platform &amp; Applications)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pensacola, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, AKS</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,19 +3331,19 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1783e76eef53a01</t>
+          <t>https://www.indeed.com/viewjob?jk=43d13a1873aa87c8</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Python Solutions Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Core BTS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a1e114754b6273</t>
+          <t>https://www.indeed.com/viewjob?jk=cb73b1bf6741a5f3</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Senior Machine Learning Engineer (NLP/LLM Focus)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Call Box</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Spark, Scala, ETL, MLOps, MLflow, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=795435ece1bb17ca</t>
+          <t>https://www.indeed.com/viewjob?jk=6fea9b3e6393fbcc</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>The Akanksha LLC</t>
+          <t>Argonne National Laboratory</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lemont, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67197d81925e64b6</t>
+          <t>https://www.indeed.com/viewjob?jk=1699fa0e2d2c879d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Engineer - Public Trust Clearance Required</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PLACE Corporate Careers</t>
+          <t>Core-CSI LLC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,17 +3461,682 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
+          <t>RDS, Azure, Spark, PySpark, Scala, Polars, ETL, ELT, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df52133313b370b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Software Engineer III-ETL/PySpark</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4852036d2a4d2871</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0bf6ee00929d1c54</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Research Triangle Park, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e729f2a707e926b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Rippling</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=744d47dbc385f247</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Northwestern Medicine</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Microsoft SSIS, Git</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c90f2bb9aa42025</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Intermediate or Sr Software Developer (AI Platform &amp; Applications)</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Dayforce</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1783e76eef53a01</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>MuleSoft Integration Architect</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Appex Innovation</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da0dc7ca51d6016c</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>MuleSoft Integration Architect</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Appex Innovation</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=594a99f1fd9583f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Full Stack Solutions Developer – Java</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=795435ece1bb17ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Azure Integration Architect</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>intent design ltd</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, NoSQL, Azure DevOps, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e7a2db86bb37412</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Azure Integration Architect</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Intent Design Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, S3, API Gateway, RDS, Azure, Scala, NoSQL, Azure DevOps, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=396b021d33329d73</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>The Akanksha LLC</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67197d81925e64b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>DevOps Architect</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Phoenix Business Consulting</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=176b1dbed7f93f82</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>MetLife</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Bridgewater, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1155785404399fad</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Blue Yonder</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afa14c95807983ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Blue Yonder</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, GitHub Actions, Docker, Kubernetes, AKS, SonarQube</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52e66699cb75c9e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Packaged/SaaS Application Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57e0eee7c9431a4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>PLACE Corporate Careers</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
           <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Docker, Git</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=94d6622d48d77919</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Python Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, Glue, S3, RDS, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4a1e114754b6273</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-28.xlsx
+++ b/results/job_matches_2026-07-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,42 +538,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Strategist - Partner</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.5</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
+          <t>AWS, Redshift, Step Functions, API Gateway, RDS, Azure, Databricks, GCP, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e8b241f5073b73</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3661ad61353f4f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a43d246f182c799</t>
+          <t>https://www.indeed.com/viewjob?jk=20e8b241f5073b73</t>
         </is>
       </c>
     </row>
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75897b83126c3579</t>
+          <t>https://www.indeed.com/viewjob?jk=9a43d246f182c799</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e92864ad72da7b0</t>
+          <t>https://www.indeed.com/viewjob?jk=75897b83126c3579</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, RDS, Google Cloud Platform, GCP</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e71e87e20fcad6</t>
+          <t>https://www.indeed.com/viewjob?jk=4e92864ad72da7b0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer- Veterans Affairs</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>THUNDERYARD SOLUTIONS</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Cloud Storage</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, RDS, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,19 +741,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b91074aae697c25</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e71e87e20fcad6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer- Veterans Affairs</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Magpie Health Analytics</t>
+          <t>THUNDERYARD SOLUTIONS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -766,77 +766,77 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SNS, RDS, Hadoop, Spark, PySpark</t>
+          <t>Kinesis, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Cloud Storage</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81821640f49f76e3</t>
+          <t>https://www.indeed.com/viewjob?jk=7b91074aae697c25</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Magpie Health Analytics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SNS, RDS, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84fb98656d187561</t>
+          <t>https://www.indeed.com/viewjob?jk=81821640f49f76e3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3d05891aeb413c</t>
+          <t>https://www.indeed.com/viewjob?jk=84fb98656d187561</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Modeler Engineer II</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29badf7873509f1c</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3d05891aeb413c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AWS Cloud Infrastructure Engineer</t>
+          <t>Business Intelligence Data Modeler Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Empower AI Inc.</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, MLOps, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34befeada094f827</t>
+          <t>https://www.indeed.com/viewjob?jk=29badf7873509f1c</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Enterprise Information Architect I</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>L.L. Bean, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Freeport, ME, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>ECS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40f6ae7d2456a50</t>
+          <t>https://www.indeed.com/viewjob?jk=cd6d7b7a1225dcc2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Enterprise Information Architect I</t>
+          <t>Spark / Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>L.L. Bean, Inc.</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Freeport, ME, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ECS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling</t>
+          <t>RDS, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd6d7b7a1225dcc2</t>
+          <t>https://www.indeed.com/viewjob?jk=e214057fae5adc71</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Sr Software Engineer - AI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Lowe's Home Improvement</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51edf63fd9ce4d7a</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1942c35e56392e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Software Engineer - AI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Lowe's Home Improvement</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd136a2c45725af</t>
+          <t>https://www.indeed.com/viewjob?jk=4b404e83cdfac818</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Spark / Databricks Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Arkansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Oracle, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e214057fae5adc71</t>
+          <t>https://www.indeed.com/viewjob?jk=511a0ee05b471605</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lowe's Home Improvement</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1942c35e56392e</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad2d81d6d9a2d31</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer - AI</t>
+          <t>Sr. Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lowe's Home Improvement</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
+          <t>AWS, Lambda, SQS, SNS, RDS, Scala, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b404e83cdfac818</t>
+          <t>https://www.indeed.com/viewjob?jk=f4591ff172a960b9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Developer – Full Stack (Java Spring Boot, React, PostgreSQL)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, MongoDB</t>
+          <t>AWS, Redshift, ECS, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad2d81d6d9a2d31</t>
+          <t>https://www.indeed.com/viewjob?jk=38439f74465262d5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer in Test</t>
+          <t>Software Developer 3 (Full Stack Developer)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Edgewater Technical Associates</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Alamos, NM, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, RDS, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4591ff172a960b9</t>
+          <t>https://www.indeed.com/viewjob?jk=64e39c95265674fb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Developer – Full Stack (Java Spring Boot, React, PostgreSQL)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38439f74465262d5</t>
+          <t>https://www.indeed.com/viewjob?jk=1c0930580a5bcd07</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Developer 3 (Full Stack Developer)</t>
+          <t>Senior Data Specialist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Edgewater Technical Associates</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Alamos, NM, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e39c95265674fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f0a26367981106</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Avantos AI</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c0930580a5bcd07</t>
+          <t>https://www.indeed.com/viewjob?jk=728e979a13366d12</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Specialist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f0a26367981106</t>
+          <t>https://www.indeed.com/viewjob?jk=b818545ba973b739</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Avantos AI</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728e979a13366d12</t>
+          <t>https://www.indeed.com/viewjob?jk=73033b8f87058bf3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>East Penn Manufacturing</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irving, NY, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b818545ba973b739</t>
+          <t>https://www.indeed.com/viewjob?jk=75e660e8c44066de</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>East Penn Manufacturing</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73033b8f87058bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=def777e7298305bd</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Security Automation &amp; SOAR Engineer</t>
+          <t>Cloud Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Kansara systems</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, ETL, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=945bfa278c31dac2</t>
+          <t>https://www.indeed.com/viewjob?jk=b0ebce6f320f9837</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>East Penn Manufacturing</t>
+          <t>Symple Lending</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, SQS, SNS, API Gateway, Scala, Kafka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e660e8c44066de</t>
+          <t>https://www.indeed.com/viewjob?jk=f3dca5d46f438997</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Software Engineer III - Big Data / AWS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>East Penn Manufacturing</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=def777e7298305bd</t>
+          <t>https://www.indeed.com/viewjob?jk=8515f265503b068a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud Developer</t>
+          <t>Software Engineer, Reconciliation &amp; Reporting</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kansara systems</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, ETL, GitHub Actions</t>
+          <t>AWS, RDS, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0ebce6f320f9837</t>
+          <t>https://www.indeed.com/viewjob?jk=9c826fbf927fd818</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Symple Lending</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, SQS, SNS, API Gateway, Scala, Kafka</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3dca5d46f438997</t>
+          <t>https://www.indeed.com/viewjob?jk=fd62b8e1edffefb2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data / AWS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8515f265503b068a</t>
+          <t>https://www.indeed.com/viewjob?jk=73c49ea64a65e4e4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer, Reconciliation &amp; Reporting</t>
+          <t>Associate Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c826fbf927fd818</t>
+          <t>https://www.indeed.com/viewjob?jk=8432eda41e25a208</t>
         </is>
       </c>
     </row>
@@ -1838,12 +1838,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd62b8e1edffefb2</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff16008b78c40ca</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73c49ea64a65e4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=2c3f08d70fed55ec</t>
         </is>
       </c>
     </row>
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8432eda41e25a208</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad10bcc1b9c0d99</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI DevOps Engineer – 1099 Contract</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Bitcot Technologies Pvt Ltd</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff16008b78c40ca</t>
+          <t>https://www.indeed.com/viewjob?jk=56400bd32a7b810d</t>
         </is>
       </c>
     </row>
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c3f08d70fed55ec</t>
+          <t>https://www.indeed.com/viewjob?jk=2c29f94189cd7da4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - GCP</t>
+          <t>Senior Technical Consultant - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad10bcc1b9c0d99</t>
+          <t>https://www.indeed.com/viewjob?jk=34f1952389da0adb</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer – 1099 Contract</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bitcot Technologies Pvt Ltd</t>
+          <t>OrangePeople</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56400bd32a7b810d</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4c6abe99182f2f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data &amp; Backend Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Chargie</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c29f94189cd7da4</t>
+          <t>https://www.indeed.com/viewjob?jk=da930629a1994ea8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer IV</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>OrangePeople</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Spark, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4c6abe99182f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=ab876d2e4fa9584b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Backend Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Chargie</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da930629a1994ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=8b99b879200d82b7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Lucet</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab876d2e4fa9584b</t>
+          <t>https://www.indeed.com/viewjob?jk=c66caa75fc25ec21</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b99b879200d82b7</t>
+          <t>https://www.indeed.com/viewjob?jk=74d507f97d89d506</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Forward Deployed Software Engineer (FDE)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Lucet</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c66caa75fc25ec21</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d38e42153f6fb0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hive, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d507f97d89d506</t>
+          <t>https://www.indeed.com/viewjob?jk=dc2a0a88a6bb4e38</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed Software Engineer (FDE)</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d38e42153f6fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=93f7c2338fe900a7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Innovative Tech Solutions</t>
+          <t>Purple Wave Auction</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77b5643dbfd08cb8</t>
+          <t>https://www.indeed.com/viewjob?jk=f455b3604d919def</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>Region 4 Education Service Center</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hive, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2a0a88a6bb4e38</t>
+          <t>https://www.indeed.com/viewjob?jk=8f972668b159bfe1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Encryption‑as‑a‑Service (EaaS) Platform Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f7c2338fe900a7</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd6c484ead70174</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Forward Deployed Engineer - AI SOC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Purple Wave Auction</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, ETL, ELT, dbt</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f455b3604d919def</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc6c1dd7963fdfd</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer III, DevOps</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Region 4 Education Service Center</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f972668b159bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=d70a210cdf39ed4c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Encryption‑as‑a‑Service (EaaS) Platform Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd6c484ead70174</t>
+          <t>https://www.indeed.com/viewjob?jk=ac2139dad458ba99</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Doggett Equipment Services Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac2139dad458ba99</t>
+          <t>https://www.indeed.com/viewjob?jk=663cb751d821c5e4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Software Engineering SMTS, Enterprise IAM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Doggett Equipment Services Group</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663cb751d821c5e4</t>
+          <t>https://www.indeed.com/viewjob?jk=eac59fd94e904980</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS, Enterprise IAM</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eac59fd94e904980</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2cf1215aaca8c2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Python Senior Developer - Data Analysis, SQL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2cf1215aaca8c2</t>
+          <t>https://www.indeed.com/viewjob?jk=630de2ec3682e100</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Python Senior Developer - Data Analysis, SQL</t>
+          <t>Sr. IT Analyst</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, ETL, ELT, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630de2ec3682e100</t>
+          <t>https://www.indeed.com/viewjob?jk=dfb5747a9d41a47e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. IT Analyst</t>
+          <t>Cloud Engineer — multi-cloud (AWS &amp; Azure), infrastructure &amp; data services</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>NeevSys</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, ETL, ELT, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfb5747a9d41a47e</t>
+          <t>https://www.indeed.com/viewjob?jk=61d9834a85f42798</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cloud Engineer — multi-cloud (AWS &amp; Azure), infrastructure &amp; data services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NeevSys</t>
+          <t>Tebra</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Corona del Mar, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, DynamoDB, CI/CD, Terraform</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d9834a85f42798</t>
+          <t>https://www.indeed.com/viewjob?jk=55760e04a88682c7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer 2- Kiewit Technology Group</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tebra</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Corona del Mar, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ELT, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55760e04a88682c7</t>
+          <t>https://www.indeed.com/viewjob?jk=e16ff09aa0b39352</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer 2- Kiewit Technology Group</t>
+          <t>Senior Systems Engineer Analyst</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>MGIC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e16ff09aa0b39352</t>
+          <t>https://www.indeed.com/viewjob?jk=c40c5bedf068bb80</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MGIC</t>
+          <t>TRIPLECOM</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>North Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40c5bedf068bb80</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e6b5d69c186e13</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Embedded Product Analytics Senior Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TRIPLECOM</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>North Brunswick, NJ, US USA</t>
+          <t>Mossville, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e6b5d69c186e13</t>
+          <t>https://www.indeed.com/viewjob?jk=01a1b2e1bcd66d65</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Embedded Product Analytics Senior Engineer</t>
+          <t>AWS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Arkatechture</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Mossville, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,19 +2981,19 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01a1b2e1bcd66d65</t>
+          <t>https://www.indeed.com/viewjob?jk=3391e6126aa7cb2b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AWS Cloud Infrastructure Engineer</t>
+          <t>Senior AI Engineer, AI Services</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Arkatechture</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, ETL, MLOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3391e6126aa7cb2b</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e6663fc1113d93</t>
         </is>
       </c>
     </row>
@@ -3688,17 +3688,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MuleSoft Integration Architect</t>
+          <t>Senior Software Engineer - Risk Technology</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,17 +3706,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Redshift, S3, RDS, Scala, Kafka, SQL Server, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0dc7ca51d6016c</t>
+          <t>https://www.indeed.com/viewjob?jk=07d2a8bd8e9419e9</t>
         </is>
       </c>
     </row>
@@ -3746,29 +3746,29 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=594a99f1fd9583f0</t>
+          <t>https://www.indeed.com/viewjob?jk=da0dc7ca51d6016c</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>MuleSoft Integration Architect</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=795435ece1bb17ca</t>
+          <t>https://www.indeed.com/viewjob?jk=594a99f1fd9583f0</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Azure Integration Architect</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>intent design ltd</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, NoSQL, Azure DevOps, Terraform, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7a2db86bb37412</t>
+          <t>https://www.indeed.com/viewjob?jk=795435ece1bb17ca</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Azure Integration Architect</t>
+          <t>DevOps Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Intent Design Pvt Ltd</t>
+          <t>Phoenix Business Consulting</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Scala, NoSQL, Azure DevOps, Terraform, Git</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=396b021d33329d73</t>
+          <t>https://www.indeed.com/viewjob?jk=176b1dbed7f93f82</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>The Akanksha LLC</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,19 +3891,19 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67197d81925e64b6</t>
+          <t>https://www.indeed.com/viewjob?jk=1155785404399fad</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Phoenix Business Consulting</t>
+          <t>Blue Yonder</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176b1dbed7f93f82</t>
+          <t>https://www.indeed.com/viewjob?jk=afa14c95807983ae</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Blue Yonder</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, GitHub Actions, Docker, Kubernetes, AKS, SonarQube</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1155785404399fad</t>
+          <t>https://www.indeed.com/viewjob?jk=52e66699cb75c9e1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Blue Yonder</t>
+          <t>The Akanksha LLC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afa14c95807983ae</t>
+          <t>https://www.indeed.com/viewjob?jk=67197d81925e64b6</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Packaged/SaaS Application Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Blue Yonder</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, GitHub Actions, Docker, Kubernetes, AKS, SonarQube</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e66699cb75c9e1</t>
+          <t>https://www.indeed.com/viewjob?jk=57e0eee7c9431a4b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Packaged/SaaS Application Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>PLACE Corporate Careers</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57e0eee7c9431a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=94d6622d48d77919</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PLACE Corporate Careers</t>
+          <t>Smart Apply Test Company</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,52 +4091,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Docker, Git</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d6622d48d77919</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Python Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, Glue, S3, RDS, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a1e114754b6273</t>
+          <t>https://www.indeed.com/viewjob?jk=cfab7796442687c5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-28.xlsx
+++ b/results/job_matches_2026-07-28.xlsx
@@ -1063,25 +1063,25 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Spark / Databricks Platform Engineer</t>
+          <t>Sr Software Engineer - AI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Lowe's Home Improvement</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e214057fae5adc71</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1942c35e56392e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - AI</t>
+          <t>Software Engineer - AI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1942c35e56392e</t>
+          <t>https://www.indeed.com/viewjob?jk=4b404e83cdfac818</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer - AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lowe's Home Improvement</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b404e83cdfac818</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad2d81d6d9a2d31</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Arkansas City, KS, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Oracle, PostgreSQL, MySQL, Cassandra</t>
+          <t>AWS, Lambda, SQS, SNS, RDS, Scala, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=511a0ee05b471605</t>
+          <t>https://www.indeed.com/viewjob?jk=f4591ff172a960b9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Developer – Full Stack (Java Spring Boot, React, PostgreSQL)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, MongoDB</t>
+          <t>AWS, Redshift, ECS, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad2d81d6d9a2d31</t>
+          <t>https://www.indeed.com/viewjob?jk=38439f74465262d5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer in Test</t>
+          <t>Software Developer 3 (Full Stack Developer)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Edgewater Technical Associates</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Alamos, NM, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, RDS, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4591ff172a960b9</t>
+          <t>https://www.indeed.com/viewjob?jk=64e39c95265674fb</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Developer – Full Stack (Java Spring Boot, React, PostgreSQL)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38439f74465262d5</t>
+          <t>https://www.indeed.com/viewjob?jk=1c0930580a5bcd07</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Developer 3 (Full Stack Developer)</t>
+          <t>Senior Data Specialist</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Edgewater Technical Associates</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Los Alamos, NM, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e39c95265674fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f0a26367981106</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Avantos AI</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c0930580a5bcd07</t>
+          <t>https://www.indeed.com/viewjob?jk=728e979a13366d12</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Specialist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f0a26367981106</t>
+          <t>https://www.indeed.com/viewjob?jk=b818545ba973b739</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Avantos AI</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728e979a13366d12</t>
+          <t>https://www.indeed.com/viewjob?jk=73033b8f87058bf3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>East Penn Manufacturing</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, NY, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b818545ba973b739</t>
+          <t>https://www.indeed.com/viewjob?jk=75e660e8c44066de</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>East Penn Manufacturing</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73033b8f87058bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=def777e7298305bd</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Cloud Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>East Penn Manufacturing</t>
+          <t>Kansara systems</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, ETL, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e660e8c44066de</t>
+          <t>https://www.indeed.com/viewjob?jk=b0ebce6f320f9837</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>East Penn Manufacturing</t>
+          <t>Symple Lending</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, SQS, SNS, API Gateway, Scala, Kafka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=def777e7298305bd</t>
+          <t>https://www.indeed.com/viewjob?jk=f3dca5d46f438997</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud Developer</t>
+          <t>Software Engineer III - Big Data / AWS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kansara systems</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, ETL, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0ebce6f320f9837</t>
+          <t>https://www.indeed.com/viewjob?jk=8515f265503b068a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>Software Engineer, Reconciliation &amp; Reporting</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Symple Lending</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, SQS, SNS, API Gateway, Scala, Kafka</t>
+          <t>AWS, RDS, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3dca5d46f438997</t>
+          <t>https://www.indeed.com/viewjob?jk=9c826fbf927fd818</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data / AWS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8515f265503b068a</t>
+          <t>https://www.indeed.com/viewjob?jk=fd62b8e1edffefb2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer, Reconciliation &amp; Reporting</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, Snowflake, ELT</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c826fbf927fd818</t>
+          <t>https://www.indeed.com/viewjob?jk=73c49ea64a65e4e4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd62b8e1edffefb2</t>
+          <t>https://www.indeed.com/viewjob?jk=8432eda41e25a208</t>
         </is>
       </c>
     </row>
@@ -1768,12 +1768,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73c49ea64a65e4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff16008b78c40ca</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - GCP</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8432eda41e25a208</t>
+          <t>https://www.indeed.com/viewjob?jk=2c3f08d70fed55ec</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff16008b78c40ca</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad10bcc1b9c0d99</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c3f08d70fed55ec</t>
+          <t>https://www.indeed.com/viewjob?jk=2c29f94189cd7da4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - GCP</t>
+          <t>Senior Technical Consultant - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad10bcc1b9c0d99</t>
+          <t>https://www.indeed.com/viewjob?jk=34f1952389da0adb</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer – 1099 Contract</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bitcot Technologies Pvt Ltd</t>
+          <t>OrangePeople</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56400bd32a7b810d</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4c6abe99182f2f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data &amp; Backend Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Chargie</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c29f94189cd7da4</t>
+          <t>https://www.indeed.com/viewjob?jk=da930629a1994ea8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Technical Consultant - Data &amp; Analytics</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34f1952389da0adb</t>
+          <t>https://www.indeed.com/viewjob?jk=8b99b879200d82b7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OrangePeople</t>
+          <t>Lucet</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4c6abe99182f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=c66caa75fc25ec21</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Backend Engineer</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Chargie</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da930629a1994ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=74d507f97d89d506</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer IV</t>
+          <t>Senior Forward Deployed Software Engineer (FDE)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab876d2e4fa9584b</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d38e42153f6fb0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hive, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,19 +2176,19 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b99b879200d82b7</t>
+          <t>https://www.indeed.com/viewjob?jk=dc2a0a88a6bb4e38</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Lucet</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2197,33 +2197,33 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c66caa75fc25ec21</t>
+          <t>https://www.indeed.com/viewjob?jk=93f7c2338fe900a7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Purple Wave Auction</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2232,11 +2232,11 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d507f97d89d506</t>
+          <t>https://www.indeed.com/viewjob?jk=f455b3604d919def</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed Software Engineer (FDE)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Region 4 Education Service Center</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d38e42153f6fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=8f972668b159bfe1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Forward Deployed Engineer - AI SOC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hive, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2a0a88a6bb4e38</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc6c1dd7963fdfd</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Engineer III, DevOps</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f7c2338fe900a7</t>
+          <t>https://www.indeed.com/viewjob?jk=d70a210cdf39ed4c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Encryption‑as‑a‑Service (EaaS) Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Purple Wave Auction</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f455b3604d919def</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd6c484ead70174</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Region 4 Education Service Center</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f972668b159bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=ac2139dad458ba99</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Encryption‑as‑a‑Service (EaaS) Platform Engineer</t>
+          <t>Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Doggett Equipment Services Group</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd6c484ead70174</t>
+          <t>https://www.indeed.com/viewjob?jk=663cb751d821c5e4</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - AI SOC</t>
+          <t>Software Engineering SMTS, Enterprise IAM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc6c1dd7963fdfd</t>
+          <t>https://www.indeed.com/viewjob?jk=eac59fd94e904980</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Engineer III, DevOps</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
+          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70a210cdf39ed4c</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2cf1215aaca8c2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Data Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac2139dad458ba99</t>
+          <t>https://www.indeed.com/viewjob?jk=322a5edbf2a5360b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Python Senior Developer - Data Analysis, SQL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Doggett Equipment Services Group</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663cb751d821c5e4</t>
+          <t>https://www.indeed.com/viewjob?jk=630de2ec3682e100</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS, Enterprise IAM</t>
+          <t>Sr. IT Analyst</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, ETL, ELT, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eac59fd94e904980</t>
+          <t>https://www.indeed.com/viewjob?jk=dfb5747a9d41a47e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Cloud Engineer — multi-cloud (AWS &amp; Azure), infrastructure &amp; data services</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>NeevSys</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2cf1215aaca8c2</t>
+          <t>https://www.indeed.com/viewjob?jk=61d9834a85f42798</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Python Senior Developer - Data Analysis, SQL</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Tebra</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Corona del Mar, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630de2ec3682e100</t>
+          <t>https://www.indeed.com/viewjob?jk=55760e04a88682c7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. IT Analyst</t>
+          <t>Software Engineer 2- Kiewit Technology Group</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, ETL, ELT, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfb5747a9d41a47e</t>
+          <t>https://www.indeed.com/viewjob?jk=e16ff09aa0b39352</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cloud Engineer — multi-cloud (AWS &amp; Azure), infrastructure &amp; data services</t>
+          <t>Senior Systems Engineer Analyst</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NeevSys</t>
+          <t>MGIC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d9834a85f42798</t>
+          <t>https://www.indeed.com/viewjob?jk=c40c5bedf068bb80</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tebra</t>
+          <t>TRIPLECOM</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Corona del Mar, CA, US USA</t>
+          <t>North Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ELT, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55760e04a88682c7</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e6b5d69c186e13</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer 2- Kiewit Technology Group</t>
+          <t>Embedded Product Analytics Senior Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Mossville, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e16ff09aa0b39352</t>
+          <t>https://www.indeed.com/viewjob?jk=01a1b2e1bcd66d65</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer Analyst</t>
+          <t>AWS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MGIC</t>
+          <t>Arkatechture</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40c5bedf068bb80</t>
+          <t>https://www.indeed.com/viewjob?jk=3391e6126aa7cb2b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer I-II, Integration Platform Engineering</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TRIPLECOM</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>North Brunswick, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e6b5d69c186e13</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbfe00edebebf90</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Embedded Product Analytics Senior Engineer</t>
+          <t>Senior AI Engineer, AI Services</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Mossville, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, ETL, MLOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01a1b2e1bcd66d65</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e6663fc1113d93</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AWS Cloud Infrastructure Engineer</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Arkatechture</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3391e6126aa7cb2b</t>
+          <t>https://www.indeed.com/viewjob?jk=502f8e4e0f72f9d7</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, AI Services</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, ETL, MLOps</t>
+          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e6663fc1113d93</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0b92db58bd05b8</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=502f8e4e0f72f9d7</t>
+          <t>https://www.indeed.com/viewjob?jk=b6cd8290f0bbfe00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>Full Stack Developer -Angular, Typescript, Bedrock</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Malvern, AR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
+          <t>AWS, RDS, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0b92db58bd05b8</t>
+          <t>https://www.indeed.com/viewjob?jk=729151ced6fff1a5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>Principle Data &amp; IT Platform Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>OxyChem</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, NoSQL, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6cd8290f0bbfe00</t>
+          <t>https://www.indeed.com/viewjob?jk=aafa6193d63da13a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full Stack Developer -Angular, Typescript, Bedrock</t>
+          <t>Software Development Engineer – Python</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Cyient</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Malvern, AR, US USA</t>
+          <t>Champaign, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=729151ced6fff1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=12dc8bc961812dc0</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Salesforce Development Engineer III</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nelnet</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44964b0a055385de</t>
+          <t>https://www.indeed.com/viewjob?jk=8e4b298a9510a69c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Principle Data &amp; IT Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>OxyChem</t>
+          <t>Nelnet</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, NoSQL, Power BI, CI/CD, Terraform</t>
+          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aafa6193d63da13a</t>
+          <t>https://www.indeed.com/viewjob?jk=44964b0a055385de</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Development Engineer – Python</t>
+          <t>Linux Systems Engineer - Server Migration</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Cyient</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Champaign, IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dc8bc961812dc0</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1c9201a8161c46</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Salesforce Development Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Pensacola, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, AKS</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4b298a9510a69c</t>
+          <t>https://www.indeed.com/viewjob?jk=43d13a1873aa87c8</t>
         </is>
       </c>
     </row>
@@ -3308,12 +3308,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Core BTS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Pensacola, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, AKS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d13a1873aa87c8</t>
+          <t>https://www.indeed.com/viewjob?jk=cb73b1bf6741a5f3</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Machine Learning Engineer (NLP/LLM Focus)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>Call Box</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Spark, Scala, ETL, MLOps, MLflow, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb73b1bf6741a5f3</t>
+          <t>https://www.indeed.com/viewjob?jk=6fea9b3e6393fbcc</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (NLP/LLM Focus)</t>
+          <t>Transportation Data Scientist</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Call Box</t>
+          <t>HNTB Corporation</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,17 +3391,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, ETL, MLOps, MLflow, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fea9b3e6393fbcc</t>
+          <t>https://www.indeed.com/viewjob?jk=62170821e4e69c98</t>
         </is>
       </c>
     </row>
@@ -3653,17 +3653,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Intermediate or Sr Software Developer (AI Platform &amp; Applications)</t>
+          <t>Senior Software Engineer - Risk Technology</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, S3, RDS, Scala, Kafka, SQL Server, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1783e76eef53a01</t>
+          <t>https://www.indeed.com/viewjob?jk=07d2a8bd8e9419e9</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Risk Technology</t>
+          <t>Intermediate or Sr Software Developer (AI Platform &amp; Applications)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,17 +3706,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, Kafka, SQL Server, CI/CD, Jenkins, Jenkins</t>
+          <t>RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d2a8bd8e9419e9</t>
+          <t>https://www.indeed.com/viewjob?jk=d1783e76eef53a01</t>
         </is>
       </c>
     </row>
@@ -3828,17 +3828,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Phoenix Business Consulting</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Kubernetes, SonarQube, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176b1dbed7f93f82</t>
+          <t>https://www.indeed.com/viewjob?jk=e01c370f5d19ca30</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>DevOps Architect</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Phoenix Business Consulting</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1155785404399fad</t>
+          <t>https://www.indeed.com/viewjob?jk=176b1dbed7f93f82</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Blue Yonder</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afa14c95807983ae</t>
+          <t>https://www.indeed.com/viewjob?jk=1155785404399fad</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, GitHub Actions, Docker, Kubernetes, AKS, SonarQube</t>
+          <t>RDS, Azure, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e66699cb75c9e1</t>
+          <t>https://www.indeed.com/viewjob?jk=afa14c95807983ae</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>The Akanksha LLC</t>
+          <t>Blue Yonder</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, GitHub Actions, Docker, Kubernetes, AKS, SonarQube</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67197d81925e64b6</t>
+          <t>https://www.indeed.com/viewjob?jk=52e66699cb75c9e1</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Packaged/SaaS Application Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>The Akanksha LLC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57e0eee7c9431a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=67197d81925e64b6</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-28.xlsx
+++ b/results/job_matches_2026-07-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Solutions Architect (Cloud Transformation)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OrangePeople</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.3</v>
+        <v>23.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,84 +496,84 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a7e6b8f9c661779</t>
+          <t>https://www.indeed.com/viewjob?jk=d09b36193d9c21c6</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Strategist - Partner</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.6</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Redshift, Step Functions, API Gateway, RDS, Azure, Databricks, GCP, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09b36193d9c21c6</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3661ad61353f4f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Strategist - Partner</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>21.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Step Functions, API Gateway, RDS, Azure, Databricks, GCP, Vertex AI, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3661ad61353f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=20e8b241f5073b73</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e8b241f5073b73</t>
+          <t>https://www.indeed.com/viewjob?jk=9a43d246f182c799</t>
         </is>
       </c>
     </row>
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a43d246f182c799</t>
+          <t>https://www.indeed.com/viewjob?jk=75897b83126c3579</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75897b83126c3579</t>
+          <t>https://www.indeed.com/viewjob?jk=4e92864ad72da7b0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer- Veterans Affairs</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>THUNDERYARD SOLUTIONS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -692,11 +692,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>Kinesis, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Cloud Storage</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e92864ad72da7b0</t>
+          <t>https://www.indeed.com/viewjob?jk=7b91074aae697c25</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Magpie Health Analytics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, RDS, Google Cloud Platform, GCP</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SNS, RDS, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e71e87e20fcad6</t>
+          <t>https://www.indeed.com/viewjob?jk=81821640f49f76e3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer- Veterans Affairs</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>THUNDERYARD SOLUTIONS</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Cloud Storage</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b91074aae697c25</t>
+          <t>https://www.indeed.com/viewjob?jk=84fb98656d187561</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Magpie Health Analytics</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SNS, RDS, Hadoop, Spark, PySpark</t>
+          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81821640f49f76e3</t>
+          <t>https://www.indeed.com/viewjob?jk=806ad6cc0b86fe80</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84fb98656d187561</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3d05891aeb413c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>AI Solutions Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -867,21 +867,21 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, Splunk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3d05891aeb413c</t>
+          <t>https://www.indeed.com/viewjob?jk=5c685db79c3a032d</t>
         </is>
       </c>
     </row>
@@ -1028,25 +1028,25 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Enterprise Information Architect I</t>
+          <t>Sr Software Engineer - AI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>L.L. Bean, Inc.</t>
+          <t>Lowe's Home Improvement</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Freeport, ME, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ECS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd6d7b7a1225dcc2</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1942c35e56392e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - AI</t>
+          <t>Software Engineer - AI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1942c35e56392e</t>
+          <t>https://www.indeed.com/viewjob?jk=4b404e83cdfac818</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer - AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lowe's Home Improvement</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Arkansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Oracle, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b404e83cdfac818</t>
+          <t>https://www.indeed.com/viewjob?jk=511a0ee05b471605</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Developer – Full Stack (Java Spring Boot, React, PostgreSQL)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, MongoDB</t>
+          <t>AWS, Redshift, ECS, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad2d81d6d9a2d31</t>
+          <t>https://www.indeed.com/viewjob?jk=38439f74465262d5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer in Test</t>
+          <t>Software Developer 3 (Full Stack Developer)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Edgewater Technical Associates</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Alamos, NM, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, RDS, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4591ff172a960b9</t>
+          <t>https://www.indeed.com/viewjob?jk=64e39c95265674fb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Developer – Full Stack (Java Spring Boot, React, PostgreSQL)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38439f74465262d5</t>
+          <t>https://www.indeed.com/viewjob?jk=1c0930580a5bcd07</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Developer 3 (Full Stack Developer)</t>
+          <t>Senior Data Specialist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Edgewater Technical Associates</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Los Alamos, NM, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e39c95265674fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f0a26367981106</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Avantos AI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c0930580a5bcd07</t>
+          <t>https://www.indeed.com/viewjob?jk=728e979a13366d12</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Specialist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f0a26367981106</t>
+          <t>https://www.indeed.com/viewjob?jk=b818545ba973b739</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Avantos AI</t>
+          <t>East Penn Manufacturing</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728e979a13366d12</t>
+          <t>https://www.indeed.com/viewjob?jk=75e660e8c44066de</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>East Penn Manufacturing</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irving, NY, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b818545ba973b739</t>
+          <t>https://www.indeed.com/viewjob?jk=def777e7298305bd</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Cloud Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>East Penn Manufacturing</t>
+          <t>Kansara systems</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, ETL, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e660e8c44066de</t>
+          <t>https://www.indeed.com/viewjob?jk=b0ebce6f320f9837</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>East Penn Manufacturing</t>
+          <t>Symple Lending</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, SQS, SNS, API Gateway, Scala, Kafka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=def777e7298305bd</t>
+          <t>https://www.indeed.com/viewjob?jk=f3dca5d46f438997</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Developer</t>
+          <t>Software Engineer III - Big Data / AWS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kansara systems</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, ETL, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0ebce6f320f9837</t>
+          <t>https://www.indeed.com/viewjob?jk=8515f265503b068a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>Software Engineer, Reconciliation &amp; Reporting</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Symple Lending</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, SQS, SNS, API Gateway, Scala, Kafka</t>
+          <t>AWS, RDS, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3dca5d46f438997</t>
+          <t>https://www.indeed.com/viewjob?jk=9c826fbf927fd818</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data / AWS</t>
+          <t>Associate Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8515f265503b068a</t>
+          <t>https://www.indeed.com/viewjob?jk=8432eda41e25a208</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer, Reconciliation &amp; Reporting</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, Snowflake, ELT</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c826fbf927fd818</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff16008b78c40ca</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd62b8e1edffefb2</t>
+          <t>https://www.indeed.com/viewjob?jk=2c3f08d70fed55ec</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73c49ea64a65e4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad10bcc1b9c0d99</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - GCP</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8432eda41e25a208</t>
+          <t>https://www.indeed.com/viewjob?jk=2c29f94189cd7da4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Technical Consultant - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff16008b78c40ca</t>
+          <t>https://www.indeed.com/viewjob?jk=34f1952389da0adb</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>OrangePeople</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c3f08d70fed55ec</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4c6abe99182f2f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - GCP</t>
+          <t>Senior Data &amp; Backend Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Chargie</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad10bcc1b9c0d99</t>
+          <t>https://www.indeed.com/viewjob?jk=da930629a1994ea8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,19 +1896,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c29f94189cd7da4</t>
+          <t>https://www.indeed.com/viewjob?jk=8b99b879200d82b7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Technical Consultant - Data &amp; Analytics</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Lucet</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34f1952389da0adb</t>
+          <t>https://www.indeed.com/viewjob?jk=c66caa75fc25ec21</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OrangePeople</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4c6abe99182f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=74d507f97d89d506</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Backend Engineer</t>
+          <t>Senior Forward Deployed Software Engineer (FDE)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Chargie</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da930629a1994ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d38e42153f6fb0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hive, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,19 +2036,19 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b99b879200d82b7</t>
+          <t>https://www.indeed.com/viewjob?jk=dc2a0a88a6bb4e38</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Lucet</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2057,33 +2057,33 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c66caa75fc25ec21</t>
+          <t>https://www.indeed.com/viewjob?jk=93f7c2338fe900a7</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Purple Wave Auction</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2092,11 +2092,11 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d507f97d89d506</t>
+          <t>https://www.indeed.com/viewjob?jk=f455b3604d919def</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed Software Engineer (FDE)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Region 4 Education Service Center</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d38e42153f6fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=8f972668b159bfe1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hive, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2a0a88a6bb4e38</t>
+          <t>https://www.indeed.com/viewjob?jk=ac2139dad458ba99</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Doggett Equipment Services Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f7c2338fe900a7</t>
+          <t>https://www.indeed.com/viewjob?jk=663cb751d821c5e4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Engineer III, DevOps</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Purple Wave Auction</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f455b3604d919def</t>
+          <t>https://www.indeed.com/viewjob?jk=d70a210cdf39ed4c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering SMTS, Enterprise IAM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Region 4 Education Service Center</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f972668b159bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=eac59fd94e904980</t>
         </is>
       </c>
     </row>
@@ -2323,60 +2323,60 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Engineer III, DevOps</t>
+          <t>Senior Data Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70a210cdf39ed4c</t>
+          <t>https://www.indeed.com/viewjob?jk=322a5edbf2a5360b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Encryption‑as‑a‑Service (EaaS) Platform Engineer</t>
+          <t>Python Senior Developer - Data Analysis, SQL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd6c484ead70174</t>
+          <t>https://www.indeed.com/viewjob?jk=630de2ec3682e100</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Sr Databricks Certified Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac2139dad458ba99</t>
+          <t>https://www.indeed.com/viewjob?jk=ba6921e4b5c7a034</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Sr. IT Analyst</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Doggett Equipment Services Group</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, ETL, ELT, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663cb751d821c5e4</t>
+          <t>https://www.indeed.com/viewjob?jk=dfb5747a9d41a47e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS, Enterprise IAM</t>
+          <t>Cloud Engineer — multi-cloud (AWS &amp; Azure), infrastructure &amp; data services</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>NeevSys</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eac59fd94e904980</t>
+          <t>https://www.indeed.com/viewjob?jk=61d9834a85f42798</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Tebra</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Corona del Mar, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, ETL, Talend</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2cf1215aaca8c2</t>
+          <t>https://www.indeed.com/viewjob?jk=55760e04a88682c7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Software Engineer - Remote</t>
+          <t>Software Engineer 2- Kiewit Technology Group</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=322a5edbf2a5360b</t>
+          <t>https://www.indeed.com/viewjob?jk=e16ff09aa0b39352</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Python Senior Developer - Data Analysis, SQL</t>
+          <t>Senior Systems Engineer Analyst</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>MGIC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630de2ec3682e100</t>
+          <t>https://www.indeed.com/viewjob?jk=c40c5bedf068bb80</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. IT Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>TRIPLECOM</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>North Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, ETL, ELT, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfb5747a9d41a47e</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e6b5d69c186e13</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cloud Engineer — multi-cloud (AWS &amp; Azure), infrastructure &amp; data services</t>
+          <t>Embedded Product Analytics Senior Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NeevSys</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mossville, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d9834a85f42798</t>
+          <t>https://www.indeed.com/viewjob?jk=01a1b2e1bcd66d65</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tebra</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Corona del Mar, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ELT, MLOps, CI/CD</t>
+          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55760e04a88682c7</t>
+          <t>https://www.indeed.com/viewjob?jk=069422425deb2f92</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer 2- Kiewit Technology Group</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e16ff09aa0b39352</t>
+          <t>https://www.indeed.com/viewjob?jk=502f8e4e0f72f9d7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer Analyst</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MGIC</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40c5bedf068bb80</t>
+          <t>https://www.indeed.com/viewjob?jk=b6cd8290f0bbfe00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TRIPLECOM</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>North Brunswick, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e6b5d69c186e13</t>
+          <t>https://www.indeed.com/viewjob?jk=ae2d8ccff2b67768</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Embedded Product Analytics Senior Engineer</t>
+          <t>Senior Software Engineer I-II, Integration Platform Engineering</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Mossville, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,29 +2831,29 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01a1b2e1bcd66d65</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbfe00edebebf90</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AWS Cloud Infrastructure Engineer</t>
+          <t>Senior AI Engineer, AI Services</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Arkatechture</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, ETL, MLOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3391e6126aa7cb2b</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e6663fc1113d93</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I-II, Integration Platform Engineering</t>
+          <t>Principle Data &amp; IT Platform Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>OxyChem</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, NoSQL, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbfe00edebebf90</t>
+          <t>https://www.indeed.com/viewjob?jk=aafa6193d63da13a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, AI Services</t>
+          <t>Software Development Engineer – Python</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Cyient</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Champaign, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, ETL, MLOps</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e6663fc1113d93</t>
+          <t>https://www.indeed.com/viewjob?jk=12dc8bc961812dc0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>Salesforce Development Engineer III</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=502f8e4e0f72f9d7</t>
+          <t>https://www.indeed.com/viewjob?jk=8e4b298a9510a69c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Nelnet</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
+          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0b92db58bd05b8</t>
+          <t>https://www.indeed.com/viewjob?jk=44964b0a055385de</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>Linux Systems Engineer - Server Migration</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,234 +3051,234 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6cd8290f0bbfe00</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1c9201a8161c46</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full Stack Developer -Angular, Typescript, Bedrock</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Malvern, AR, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=729151ced6fff1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=d7a2187db3c65150</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Principle Data &amp; IT Platform Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>OxyChem</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, NoSQL, Power BI, CI/CD, Terraform</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aafa6193d63da13a</t>
+          <t>https://www.indeed.com/viewjob?jk=271ee7fda7a6bee4</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Development Engineer – Python</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cyient</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Champaign, IL, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dc8bc961812dc0</t>
+          <t>https://www.indeed.com/viewjob?jk=dee5bdcb019976f9</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Salesforce Development Engineer III</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4b298a9510a69c</t>
+          <t>https://www.indeed.com/viewjob?jk=eae6cbdf5a874676</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nelnet</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44964b0a055385de</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a7b2f239e82d02</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Linux Systems Engineer - Server Migration</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1c9201a8161c46</t>
+          <t>https://www.indeed.com/viewjob?jk=da1b3b3f4ca0ce2d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Pensacola, FL, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, AKS</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d13a1873aa87c8</t>
+          <t>https://www.indeed.com/viewjob?jk=2153d438774a509a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb73b1bf6741a5f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c4985d9926908755</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (NLP/LLM Focus)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Call Box</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, ETL, MLOps, MLflow, Terraform, Docker</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fea9b3e6393fbcc</t>
+          <t>https://www.indeed.com/viewjob?jk=a8c4f97707d87774</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Transportation Data Scientist</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>HNTB Corporation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62170821e4e69c98</t>
+          <t>https://www.indeed.com/viewjob?jk=f38308f7020f4ab6</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Argonne National Laboratory</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Lemont, IL, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1699fa0e2d2c879d</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2848e822349e37</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Public Trust Clearance Required</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Core-CSI LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Polars, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df52133313b370b6</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd7c699bcfc3b5b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4852036d2a4d2871</t>
+          <t>https://www.indeed.com/viewjob?jk=31cc678d8a1b36d2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf6ee00929d1c54</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a81eae23fb3d49</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e729f2a707e926b3</t>
+          <t>https://www.indeed.com/viewjob?jk=e650c829a90727ae</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744d47dbc385f247</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f80c3b16775bd9</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Northwestern Medicine</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Microsoft SSIS, Git</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c90f2bb9aa42025</t>
+          <t>https://www.indeed.com/viewjob?jk=d7c9c591b425e81f</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Risk Technology</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, Kafka, SQL Server, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d2a8bd8e9419e9</t>
+          <t>https://www.indeed.com/viewjob?jk=c2086bcd7f5b4a23</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Intermediate or Sr Software Developer (AI Platform &amp; Applications)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1783e76eef53a01</t>
+          <t>https://www.indeed.com/viewjob?jk=1a8bc962520011e7</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MuleSoft Integration Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0dc7ca51d6016c</t>
+          <t>https://www.indeed.com/viewjob?jk=6e29721616c97913</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MuleSoft Integration Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=594a99f1fd9583f0</t>
+          <t>https://www.indeed.com/viewjob?jk=0956fb4c5c9c0552</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=795435ece1bb17ca</t>
+          <t>https://www.indeed.com/viewjob?jk=0691a1c6266d435b</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Kubernetes, SonarQube, Git</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e01c370f5d19ca30</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a249a14145a4a4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Phoenix Business Consulting</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176b1dbed7f93f82</t>
+          <t>https://www.indeed.com/viewjob?jk=70aa2099184a5196</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1155785404399fad</t>
+          <t>https://www.indeed.com/viewjob?jk=059536b8aca9d2a2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Blue Yonder</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afa14c95807983ae</t>
+          <t>https://www.indeed.com/viewjob?jk=558ed485df852c51</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Blue Yonder</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, GitHub Actions, Docker, Kubernetes, AKS, SonarQube</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e66699cb75c9e1</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0e1e7cdd67ce1c</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>The Akanksha LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67197d81925e64b6</t>
+          <t>https://www.indeed.com/viewjob?jk=f7fb9b2593fe48de</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PLACE Corporate Careers</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,50 +4056,1590 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Docker, Git</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d6622d48d77919</t>
+          <t>https://www.indeed.com/viewjob?jk=4f770060507dc86b</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>NV, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f1a4c01874e8f79</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>WV, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af904feccae24be9</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>WI, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c4d3fcf499932c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ME, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa87bd48c2643a2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ID, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee0798b4cd7fde41</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>KS, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0a59ae85c3362ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2e02fbdbb185ec1</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>MS, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e53a0405898f435</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>OK, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0a18c489a6677b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>MO, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d36053a9cd0e254a</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ffc19476000a7ec6</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e4d40dfe7f3c0d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>MN, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=36bb93a99e60b085</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>NE, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43939234e151d703</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e67f673abfada57e</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>VT, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6c09cdff3fed03d</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>NM, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0042baaea7e63584</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>AR, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=583da55552160f98</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cd52ee12f4c5cea</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d03eb01083cb07bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Navy Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Pensacola, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, AKS</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43d13a1873aa87c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer (NLP/LLM Focus)</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Call Box</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Spark, Scala, ETL, MLOps, MLflow, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6fea9b3e6393fbcc</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Transportation Data Scientist</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>HNTB Corporation</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Downers Grove, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62170821e4e69c98</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Argonne National Laboratory</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Lemont, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1699fa0e2d2c879d</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Public Trust Clearance Required</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Core-CSI LLC</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, PySpark, Scala, Polars, ETL, ELT, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df52133313b370b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Software Engineer III-ETL/PySpark</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4852036d2a4d2871</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0bf6ee00929d1c54</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Research Triangle Park, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e729f2a707e926b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Rippling</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=744d47dbc385f247</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Forward Deployment Engineer</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Global KTech</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1aab47487016cd9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>MuleSoft Integration Architect</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Appex Innovation</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da0dc7ca51d6016c</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>MuleSoft Integration Architect</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Appex Innovation</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=594a99f1fd9583f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Intermediate or Sr Software Developer (AI Platform &amp; Applications)</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Dayforce</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1783e76eef53a01</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Full Stack Solutions Developer – Java</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=795435ece1bb17ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Sr Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, Azure, Vertex AI, Spark, Scala, Kafka, DynamoDB, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a16a037aab83b32</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Risk Technology</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Millennium Management</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, S3, RDS, Scala, Kafka, SQL Server, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07d2a8bd8e9419e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Research Scientist II, Step 1-4</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>University of Alabama in Huntsville</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>AL, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b876b59e168c817</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Sr Mgr, Software Engineering</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Disney Experiences</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Power BI, Tableau, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1779138f771f4150</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Senior Technical Architect</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>HCLTech</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Kubernetes, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e01c370f5d19ca30</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>DevOps Architect</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Phoenix Business Consulting</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=176b1dbed7f93f82</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>MetLife</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Bridgewater, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1155785404399fad</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Blue Yonder</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afa14c95807983ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Blue Yonder</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, GitHub Actions, Docker, Kubernetes, AKS, SonarQube</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52e66699cb75c9e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>PLACE Corporate Careers</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94d6622d48d77919</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
           <t>Software Engineer – Full Stack</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B149" t="inlineStr">
         <is>
           <t>Smart Apply Test Company</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C149" t="inlineStr">
         <is>
           <t>Tampa, FL, US USA</t>
         </is>
       </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
         <is>
           <t>AWS, Lambda, S3, SQS, SNS, API Gateway, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cfab7796442687c5</t>
         </is>

--- a/results/job_matches_2026-07-28.xlsx
+++ b/results/job_matches_2026-07-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G149"/>
+  <dimension ref="A1:G152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,47 +678,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer- Veterans Affairs</t>
+          <t>Data and Analytics Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>THUNDERYARD SOLUTIONS</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Cloud Storage</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b91074aae697c25</t>
+          <t>https://www.indeed.com/viewjob?jk=6fca29e64567b9a7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer- Veterans Affairs</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Magpie Health Analytics</t>
+          <t>THUNDERYARD SOLUTIONS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -731,104 +731,104 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SNS, RDS, Hadoop, Spark, PySpark</t>
+          <t>Kinesis, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Cloud Storage</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81821640f49f76e3</t>
+          <t>https://www.indeed.com/viewjob?jk=7b91074aae697c25</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Magpie Health Analytics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SNS, RDS, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84fb98656d187561</t>
+          <t>https://www.indeed.com/viewjob?jk=81821640f49f76e3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=806ad6cc0b86fe80</t>
+          <t>https://www.indeed.com/viewjob?jk=84fb98656d187561</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,29 +836,29 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3d05891aeb413c</t>
+          <t>https://www.indeed.com/viewjob?jk=806ad6cc0b86fe80</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Solutions Architect</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -867,81 +867,81 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, Splunk</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c685db79c3a032d</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3d05891aeb413c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Modeler Engineer II</t>
+          <t>AI Solutions Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, Splunk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29badf7873509f1c</t>
+          <t>https://www.indeed.com/viewjob?jk=5c685db79c3a032d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Intelligence Data Modeler Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e3771f0c36b6f26</t>
+          <t>https://www.indeed.com/viewjob?jk=29badf7873509f1c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f88f3978f6e2de83</t>
+          <t>https://www.indeed.com/viewjob?jk=5e3771f0c36b6f26</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BI Data Engineer II</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Boston Beer Company</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62785c4010471f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=f88f3978f6e2de83</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - AI</t>
+          <t>BI Data Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lowe's Home Improvement</t>
+          <t>The Boston Beer Company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1942c35e56392e</t>
+          <t>https://www.indeed.com/viewjob?jk=62785c4010471f7c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer - AI</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lowe's Home Improvement</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b404e83cdfac818</t>
+          <t>https://www.indeed.com/viewjob?jk=a40f6ae7d2456a50</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Arkansas City, KS, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Oracle, PostgreSQL, MySQL, Cassandra</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=511a0ee05b471605</t>
+          <t>https://www.indeed.com/viewjob?jk=51edf63fd9ce4d7a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Developer – Full Stack (Java Spring Boot, React, PostgreSQL)</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38439f74465262d5</t>
+          <t>https://www.indeed.com/viewjob?jk=acd136a2c45725af</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Developer 3 (Full Stack Developer)</t>
+          <t>Sr Hadoop+Spark(scala) Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Edgewater Technical Associates</t>
+          <t>Virtues</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Los Alamos, NM, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e39c95265674fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8aeb2bc3ba9b6d82</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Sr Software Engineer - AI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Lowe's Home Improvement</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c0930580a5bcd07</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1942c35e56392e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Specialist</t>
+          <t>Software Engineer - AI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Lowe's Home Improvement</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f0a26367981106</t>
+          <t>https://www.indeed.com/viewjob?jk=4b404e83cdfac818</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Avantos AI</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arkansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Oracle, PostgreSQL, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728e979a13366d12</t>
+          <t>https://www.indeed.com/viewjob?jk=511a0ee05b471605</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior MuleSoft Integration Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>VGMT GLOBAL IT SOLUTIONS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irving, NY, US USA</t>
+          <t>Goldsmith, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b818545ba973b739</t>
+          <t>https://www.indeed.com/viewjob?jk=2b0fefd7a48d7cb0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Senior Developer – Full Stack (Java Spring Boot, React, PostgreSQL)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>East Penn Manufacturing</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Redshift, ECS, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e660e8c44066de</t>
+          <t>https://www.indeed.com/viewjob?jk=38439f74465262d5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Software Developer 3 (Full Stack Developer)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>East Penn Manufacturing</t>
+          <t>Edgewater Technical Associates</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Los Alamos, NM, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=def777e7298305bd</t>
+          <t>https://www.indeed.com/viewjob?jk=64e39c95265674fb</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73033b8f87058bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=1c0930580a5bcd07</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kansara systems</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, NoSQL, Data Modeling, ETL, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0ebce6f320f9837</t>
+          <t>https://www.indeed.com/viewjob?jk=48a21bba741abb42</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>Analyst Databricks</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Symple Lending</t>
+          <t>Hilton Grand Vacations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,42 +1501,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, SQS, SNS, API Gateway, Scala, Kafka</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3dca5d46f438997</t>
+          <t>https://www.indeed.com/viewjob?jk=79bb920959efbb9a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data / AWS</t>
+          <t>Senior Data Specialist</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8515f265503b068a</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f0a26367981106</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer, Reconciliation &amp; Reporting</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Avantos AI</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c826fbf927fd818</t>
+          <t>https://www.indeed.com/viewjob?jk=728e979a13366d12</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - GCP</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1598,15 +1598,15 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8432eda41e25a208</t>
+          <t>https://www.indeed.com/viewjob?jk=b818545ba973b739</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff16008b78c40ca</t>
+          <t>https://www.indeed.com/viewjob?jk=73033b8f87058bf3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>East Penn Manufacturing</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c3f08d70fed55ec</t>
+          <t>https://www.indeed.com/viewjob?jk=75e660e8c44066de</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - GCP</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>East Penn Manufacturing</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad10bcc1b9c0d99</t>
+          <t>https://www.indeed.com/viewjob?jk=def777e7298305bd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Symple Lending</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, SQS, SNS, API Gateway, Scala, Kafka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c29f94189cd7da4</t>
+          <t>https://www.indeed.com/viewjob?jk=f3dca5d46f438997</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Technical Consultant - Data &amp; Analytics</t>
+          <t>Software Engineer III - Big Data / AWS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34f1952389da0adb</t>
+          <t>https://www.indeed.com/viewjob?jk=8515f265503b068a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer, Reconciliation &amp; Reporting</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>OrangePeople</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4c6abe99182f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=9c826fbf927fd818</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Backend Engineer</t>
+          <t>Associate Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Chargie</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da930629a1994ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=8432eda41e25a208</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b99b879200d82b7</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff16008b78c40ca</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lucet</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, SQL Server, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c66caa75fc25ec21</t>
+          <t>https://www.indeed.com/viewjob?jk=2c3f08d70fed55ec</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d507f97d89d506</t>
+          <t>https://www.indeed.com/viewjob?jk=2c29f94189cd7da4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed Software Engineer (FDE)</t>
+          <t>Senior Technical Consultant - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,42 +1991,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d38e42153f6fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=34f1952389da0adb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>OrangePeople</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hive, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2a0a88a6bb4e38</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4c6abe99182f2f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Senior Data &amp; Backend Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Chargie</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f7c2338fe900a7</t>
+          <t>https://www.indeed.com/viewjob?jk=da930629a1994ea8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Purple Wave Auction</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,137 +2106,137 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f455b3604d919def</t>
+          <t>https://www.indeed.com/viewjob?jk=8b99b879200d82b7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Region 4 Education Service Center</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f972668b159bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=eee6148be255d369</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac2139dad458ba99</t>
+          <t>https://www.indeed.com/viewjob?jk=a8fc463b1f1234a3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Doggett Equipment Services Group</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663cb751d821c5e4</t>
+          <t>https://www.indeed.com/viewjob?jk=9f93d9150c8d68a7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Engineer III, DevOps</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70a210cdf39ed4c</t>
+          <t>https://www.indeed.com/viewjob?jk=74d507f97d89d506</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS, Enterprise IAM</t>
+          <t>Senior Forward Deployed Software Engineer (FDE)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eac59fd94e904980</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d38e42153f6fb0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - AI SOC</t>
+          <t>I O Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, S3, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc6c1dd7963fdfd</t>
+          <t>https://www.indeed.com/viewjob?jk=882309c5e77e174d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Software Engineer - Remote</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=322a5edbf2a5360b</t>
+          <t>https://www.indeed.com/viewjob?jk=93f7c2338fe900a7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Python Senior Developer - Data Analysis, SQL</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Purple Wave Auction</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,102 +2386,102 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630de2ec3682e100</t>
+          <t>https://www.indeed.com/viewjob?jk=f455b3604d919def</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr Databricks Certified Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>Region 4 Education Service Center</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba6921e4b5c7a034</t>
+          <t>https://www.indeed.com/viewjob?jk=8f972668b159bfe1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. IT Analyst</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>SEI Investments</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, ETL, ELT, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, Azure, Snowflake, Oracle, SQL Server, MySQL, MongoDB, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfb5747a9d41a47e</t>
+          <t>https://www.indeed.com/viewjob?jk=3d91881ede271802</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cloud Engineer — multi-cloud (AWS &amp; Azure), infrastructure &amp; data services</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NeevSys</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d9834a85f42798</t>
+          <t>https://www.indeed.com/viewjob?jk=ac2139dad458ba99</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tebra</t>
+          <t>Doggett Equipment Services Group</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Corona del Mar, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ELT, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55760e04a88682c7</t>
+          <t>https://www.indeed.com/viewjob?jk=663cb751d821c5e4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer 2- Kiewit Technology Group</t>
+          <t>Engineer III, DevOps</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e16ff09aa0b39352</t>
+          <t>https://www.indeed.com/viewjob?jk=d70a210cdf39ed4c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer Analyst</t>
+          <t>Software Engineering SMTS, Enterprise IAM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MGIC</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,59 +2596,59 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40c5bedf068bb80</t>
+          <t>https://www.indeed.com/viewjob?jk=eac59fd94e904980</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Forward Deployed Engineer - AI SOC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TRIPLECOM</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>North Brunswick, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e6b5d69c186e13</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc6c1dd7963fdfd</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Embedded Product Analytics Senior Engineer</t>
+          <t>Senior Data Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Mossville, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01a1b2e1bcd66d65</t>
+          <t>https://www.indeed.com/viewjob?jk=322a5edbf2a5360b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>Sr Databricks Certified Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=069422425deb2f92</t>
+          <t>https://www.indeed.com/viewjob?jk=ba6921e4b5c7a034</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>Sr. IT Analyst</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, ETL, ELT, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=502f8e4e0f72f9d7</t>
+          <t>https://www.indeed.com/viewjob?jk=dfb5747a9d41a47e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>Cloud Engineer — multi-cloud (AWS &amp; Azure), infrastructure &amp; data services</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>NeevSys</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6cd8290f0bbfe00</t>
+          <t>https://www.indeed.com/viewjob?jk=61d9834a85f42798</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - QuantumBlack, AI by McKinsey</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Tebra</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Corona del Mar, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae2d8ccff2b67768</t>
+          <t>https://www.indeed.com/viewjob?jk=55760e04a88682c7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I-II, Integration Platform Engineering</t>
+          <t>Software Engineer 2- Kiewit Technology Group</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbfe00edebebf90</t>
+          <t>https://www.indeed.com/viewjob?jk=e16ff09aa0b39352</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, AI Services</t>
+          <t>Senior Systems Engineer Analyst</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>MGIC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, ETL, MLOps</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e6663fc1113d93</t>
+          <t>https://www.indeed.com/viewjob?jk=c40c5bedf068bb80</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Principle Data &amp; IT Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>OxyChem</t>
+          <t>TRIPLECOM</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>North Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, NoSQL, Power BI, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aafa6193d63da13a</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e6b5d69c186e13</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Development Engineer – Python</t>
+          <t>Embedded Product Analytics Senior Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cyient</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Champaign, IL, US USA</t>
+          <t>Mossville, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dc8bc961812dc0</t>
+          <t>https://www.indeed.com/viewjob?jk=01a1b2e1bcd66d65</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Salesforce Development Engineer III</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4b298a9510a69c</t>
+          <t>https://www.indeed.com/viewjob?jk=069422425deb2f92</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Nelnet</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44964b0a055385de</t>
+          <t>https://www.indeed.com/viewjob?jk=ae2d8ccff2b67768</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Linux Systems Engineer - Server Migration</t>
+          <t>Senior Software Engineer I-II, Integration Platform Engineering</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,42 +3041,42 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1c9201a8161c46</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbfe00edebebf90</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior AI Engineer, AI Services</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, ETL, MLOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,269 +3086,269 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7a2187db3c65150</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e6663fc1113d93</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271ee7fda7a6bee4</t>
+          <t>https://www.indeed.com/viewjob?jk=502f8e4e0f72f9d7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee5bdcb019976f9</t>
+          <t>https://www.indeed.com/viewjob?jk=b6cd8290f0bbfe00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Principle Data &amp; IT Platform Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>OxyChem</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, NoSQL, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae6cbdf5a874676</t>
+          <t>https://www.indeed.com/viewjob?jk=aafa6193d63da13a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Development Engineer – Python</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cyient</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>Champaign, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a7b2f239e82d02</t>
+          <t>https://www.indeed.com/viewjob?jk=12dc8bc961812dc0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Salesforce Development Engineer III</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1b3b3f4ca0ce2d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e4b298a9510a69c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Nelnet</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2153d438774a509a</t>
+          <t>https://www.indeed.com/viewjob?jk=44964b0a055385de</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Linux Systems Engineer - Server Migration</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4985d9926908755</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1c9201a8161c46</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Software Engineer (Data)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Solovis</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Scala, PostgreSQL, ETL, ELT, CI/CD, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8c4f97707d87774</t>
+          <t>https://www.indeed.com/viewjob?jk=c802ebbce7a223a1</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f38308f7020f4ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=d7a2187db3c65150</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2848e822349e37</t>
+          <t>https://www.indeed.com/viewjob?jk=271ee7fda7a6bee4</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd7c699bcfc3b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=dee5bdcb019976f9</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31cc678d8a1b36d2</t>
+          <t>https://www.indeed.com/viewjob?jk=eae6cbdf5a874676</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a81eae23fb3d49</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a7b2f239e82d02</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e650c829a90727ae</t>
+          <t>https://www.indeed.com/viewjob?jk=da1b3b3f4ca0ce2d</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f80c3b16775bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=2153d438774a509a</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7c9c591b425e81f</t>
+          <t>https://www.indeed.com/viewjob?jk=c4985d9926908755</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2086bcd7f5b4a23</t>
+          <t>https://www.indeed.com/viewjob?jk=a8c4f97707d87774</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a8bc962520011e7</t>
+          <t>https://www.indeed.com/viewjob?jk=f38308f7020f4ab6</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e29721616c97913</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2848e822349e37</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0956fb4c5c9c0552</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd7c699bcfc3b5b</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0691a1c6266d435b</t>
+          <t>https://www.indeed.com/viewjob?jk=31cc678d8a1b36d2</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a249a14145a4a4</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a81eae23fb3d49</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70aa2099184a5196</t>
+          <t>https://www.indeed.com/viewjob?jk=e650c829a90727ae</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059536b8aca9d2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f80c3b16775bd9</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558ed485df852c51</t>
+          <t>https://www.indeed.com/viewjob?jk=d7c9c591b425e81f</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0e1e7cdd67ce1c</t>
+          <t>https://www.indeed.com/viewjob?jk=c2086bcd7f5b4a23</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7fb9b2593fe48de</t>
+          <t>https://www.indeed.com/viewjob?jk=1a8bc962520011e7</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f770060507dc86b</t>
+          <t>https://www.indeed.com/viewjob?jk=6e29721616c97913</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f1a4c01874e8f79</t>
+          <t>https://www.indeed.com/viewjob?jk=0956fb4c5c9c0552</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af904feccae24be9</t>
+          <t>https://www.indeed.com/viewjob?jk=0691a1c6266d435b</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c4d3fcf499932c1</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a249a14145a4a4</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa87bd48c2643a2c</t>
+          <t>https://www.indeed.com/viewjob?jk=70aa2099184a5196</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee0798b4cd7fde41</t>
+          <t>https://www.indeed.com/viewjob?jk=059536b8aca9d2a2</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a59ae85c3362ed</t>
+          <t>https://www.indeed.com/viewjob?jk=558ed485df852c51</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e02fbdbb185ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0e1e7cdd67ce1c</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e53a0405898f435</t>
+          <t>https://www.indeed.com/viewjob?jk=f7fb9b2593fe48de</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a18c489a6677b2</t>
+          <t>https://www.indeed.com/viewjob?jk=4f770060507dc86b</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d36053a9cd0e254a</t>
+          <t>https://www.indeed.com/viewjob?jk=9f1a4c01874e8f79</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc19476000a7ec6</t>
+          <t>https://www.indeed.com/viewjob?jk=af904feccae24be9</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e4d40dfe7f3c0d8</t>
+          <t>https://www.indeed.com/viewjob?jk=1c4d3fcf499932c1</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36bb93a99e60b085</t>
+          <t>https://www.indeed.com/viewjob?jk=fa87bd48c2643a2c</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43939234e151d703</t>
+          <t>https://www.indeed.com/viewjob?jk=ee0798b4cd7fde41</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e67f673abfada57e</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a59ae85c3362ed</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6c09cdff3fed03d</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e02fbdbb185ec1</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0042baaea7e63584</t>
+          <t>https://www.indeed.com/viewjob?jk=4e53a0405898f435</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583da55552160f98</t>
+          <t>https://www.indeed.com/viewjob?jk=b0a18c489a6677b2</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd52ee12f4c5cea</t>
+          <t>https://www.indeed.com/viewjob?jk=d36053a9cd0e254a</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d03eb01083cb07bd</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc19476000a7ec6</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Pensacola, FL, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, AKS</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d13a1873aa87c8</t>
+          <t>https://www.indeed.com/viewjob?jk=5e4d40dfe7f3c0d8</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (NLP/LLM Focus)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Call Box</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, ETL, MLOps, MLflow, Terraform, Docker</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fea9b3e6393fbcc</t>
+          <t>https://www.indeed.com/viewjob?jk=36bb93a99e60b085</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Transportation Data Scientist</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>HNTB Corporation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62170821e4e69c98</t>
+          <t>https://www.indeed.com/viewjob?jk=43939234e151d703</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Argonne National Laboratory</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Lemont, IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1699fa0e2d2c879d</t>
+          <t>https://www.indeed.com/viewjob?jk=e67f673abfada57e</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Public Trust Clearance Required</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Core-CSI LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Polars, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df52133313b370b6</t>
+          <t>https://www.indeed.com/viewjob?jk=d6c09cdff3fed03d</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4852036d2a4d2871</t>
+          <t>https://www.indeed.com/viewjob?jk=0042baaea7e63584</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf6ee00929d1c54</t>
+          <t>https://www.indeed.com/viewjob?jk=583da55552160f98</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e729f2a707e926b3</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd52ee12f4c5cea</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=744d47dbc385f247</t>
+          <t>https://www.indeed.com/viewjob?jk=d03eb01083cb07bd</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Global KTech</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pensacola, FL, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, AKS</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aab47487016cd9b</t>
+          <t>https://www.indeed.com/viewjob?jk=43d13a1873aa87c8</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MuleSoft Integration Architect</t>
+          <t>Senior Machine Learning Engineer (NLP/LLM Focus)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>Call Box</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Spark, Scala, ETL, MLOps, MLflow, Terraform, Docker</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0dc7ca51d6016c</t>
+          <t>https://www.indeed.com/viewjob?jk=6fea9b3e6393fbcc</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MuleSoft Integration Architect</t>
+          <t>Transportation Data Scientist</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>HNTB Corporation</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=594a99f1fd9583f0</t>
+          <t>https://www.indeed.com/viewjob?jk=62170821e4e69c98</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Intermediate or Sr Software Developer (AI Platform &amp; Applications)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Argonne National Laboratory</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lemont, IL, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1783e76eef53a01</t>
+          <t>https://www.indeed.com/viewjob?jk=1699fa0e2d2c879d</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Senior Data Engineer - Public Trust Clearance Required</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Core-CSI LLC</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Polars, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=795435ece1bb17ca</t>
+          <t>https://www.indeed.com/viewjob?jk=df52133313b370b6</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Software Engineer III-ETL/PySpark</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Vertex AI, Spark, Scala, Kafka, DynamoDB, Terraform, Docker</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a16a037aab83b32</t>
+          <t>https://www.indeed.com/viewjob?jk=4852036d2a4d2871</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Risk Technology</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, Kafka, SQL Server, CI/CD, Jenkins, Jenkins</t>
+          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d2a8bd8e9419e9</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf6ee00929d1c54</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Research Scientist II, Step 1-4</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>University of Alabama in Huntsville</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git, Python, SQL</t>
+          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b876b59e168c817</t>
+          <t>https://www.indeed.com/viewjob?jk=e729f2a707e926b3</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Sr Mgr, Software Engineering</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Power BI, Tableau, Airflow, Apache Airflow</t>
+          <t>AWS, Kinesis, Azure, Vertex AI, Spark, Scala, Kafka, DynamoDB, Terraform, Docker</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1779138f771f4150</t>
+          <t>https://www.indeed.com/viewjob?jk=1a16a037aab83b32</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Senior Software Engineer - Risk Technology</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Kubernetes, SonarQube, Git</t>
+          <t>AWS, Redshift, S3, RDS, Scala, Kafka, SQL Server, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e01c370f5d19ca30</t>
+          <t>https://www.indeed.com/viewjob?jk=07d2a8bd8e9419e9</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>Research Scientist II, Step 1-4</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Phoenix Business Consulting</t>
+          <t>University of Alabama in Huntsville</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176b1dbed7f93f82</t>
+          <t>https://www.indeed.com/viewjob?jk=4b876b59e168c817</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Sr Mgr, Software Engineering</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Power BI, Tableau, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1155785404399fad</t>
+          <t>https://www.indeed.com/viewjob?jk=1779138f771f4150</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Blue Yonder</t>
+          <t>Global KTech</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afa14c95807983ae</t>
+          <t>https://www.indeed.com/viewjob?jk=1aab47487016cd9b</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>MuleSoft Integration Architect</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Blue Yonder</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, GitHub Actions, Docker, Kubernetes, AKS, SonarQube</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e66699cb75c9e1</t>
+          <t>https://www.indeed.com/viewjob?jk=da0dc7ca51d6016c</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>MuleSoft Integration Architect</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PLACE Corporate Careers</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,40 +5606,145 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d6622d48d77919</t>
+          <t>https://www.indeed.com/viewjob?jk=594a99f1fd9583f0</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
+          <t>Intermediate or Sr Software Developer (AI Platform &amp; Applications)</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Dayforce</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1783e76eef53a01</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Full Stack Solutions Developer – Java</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=795435ece1bb17ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Senior Technical Architect</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>HCLTech</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Kubernetes, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e01c370f5d19ca30</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
           <t>Software Engineer – Full Stack</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="B152" t="inlineStr">
         <is>
           <t>Smart Apply Test Company</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
+      <c r="C152" t="inlineStr">
         <is>
           <t>Tampa, FL, US USA</t>
         </is>
       </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
         <is>
           <t>AWS, Lambda, S3, SQS, SNS, API Gateway, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cfab7796442687c5</t>
         </is>

--- a/results/job_matches_2026-07-28.xlsx
+++ b/results/job_matches_2026-07-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G152"/>
+  <dimension ref="A1:G155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,12 +473,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,94 +486,94 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09b36193d9c21c6</t>
+          <t>https://www.indeed.com/viewjob?jk=56a2ba898cd68ef3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Strategist - Partner</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>23.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Step Functions, API Gateway, RDS, Azure, Databricks, GCP, Vertex AI, Spark</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3661ad61353f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=d09b36193d9c21c6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Strategist - Partner</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.5</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
+          <t>AWS, Redshift, Step Functions, API Gateway, RDS, Azure, Databricks, GCP, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e8b241f5073b73</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3661ad61353f4f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a43d246f182c799</t>
+          <t>https://www.indeed.com/viewjob?jk=20e8b241f5073b73</t>
         </is>
       </c>
     </row>
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75897b83126c3579</t>
+          <t>https://www.indeed.com/viewjob?jk=9a43d246f182c799</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e92864ad72da7b0</t>
+          <t>https://www.indeed.com/viewjob?jk=75897b83126c3579</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data and Analytics Architect</t>
+          <t>Senior Integration Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>EDRAY</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.4</v>
+        <v>20.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fca29e64567b9a7</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd9bc76eb207693</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer- Veterans Affairs</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>THUNDERYARD SOLUTIONS</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Cloud Storage</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b91074aae697c25</t>
+          <t>https://www.indeed.com/viewjob?jk=4e92864ad72da7b0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data and Analytics Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Magpie Health Analytics</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SNS, RDS, Hadoop, Spark, PySpark</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81821640f49f76e3</t>
+          <t>https://www.indeed.com/viewjob?jk=6fca29e64567b9a7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer- Veterans Affairs</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>THUNDERYARD SOLUTIONS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>Kinesis, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Cloud Storage</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84fb98656d187561</t>
+          <t>https://www.indeed.com/viewjob?jk=7b91074aae697c25</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Magpie Health Analytics</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SNS, RDS, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=806ad6cc0b86fe80</t>
+          <t>https://www.indeed.com/viewjob?jk=81821640f49f76e3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3d05891aeb413c</t>
+          <t>https://www.indeed.com/viewjob?jk=84fb98656d187561</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Solutions Architect</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, Splunk</t>
+          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c685db79c3a032d</t>
+          <t>https://www.indeed.com/viewjob?jk=806ad6cc0b86fe80</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Modeler Engineer II</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,19 +951,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29badf7873509f1c</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3d05891aeb413c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Solutions Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -972,46 +972,46 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, Splunk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e3771f0c36b6f26</t>
+          <t>https://www.indeed.com/viewjob?jk=5c685db79c3a032d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Business Intelligence Data Modeler Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f88f3978f6e2de83</t>
+          <t>https://www.indeed.com/viewjob?jk=29badf7873509f1c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BI Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Boston Beer Company</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62785c4010471f7c</t>
+          <t>https://www.indeed.com/viewjob?jk=5e3771f0c36b6f26</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior MuleSoft Integration Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>VGMT GLOBAL IT SOLUTIONS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Arkansas City, KS, US USA</t>
+          <t>Goldsmith, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Oracle, PostgreSQL, MySQL, Cassandra</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=511a0ee05b471605</t>
+          <t>https://www.indeed.com/viewjob?jk=2b0fefd7a48d7cb0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Integration Developer</t>
+          <t>Software Developer 3 (Full Stack Developer)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VGMT GLOBAL IT SOLUTIONS</t>
+          <t>Edgewater Technical Associates</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Goldsmith, TX, US USA</t>
+          <t>Los Alamos, NM, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,112 +1326,112 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0fefd7a48d7cb0</t>
+          <t>https://www.indeed.com/viewjob?jk=64e39c95265674fb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Developer – Full Stack (Java Spring Boot, React, PostgreSQL)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, ECS, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38439f74465262d5</t>
+          <t>https://www.indeed.com/viewjob?jk=48a21bba741abb42</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Developer 3 (Full Stack Developer)</t>
+          <t>Analyst Databricks</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Edgewater Technical Associates</t>
+          <t>Hilton Grand Vacations</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Alamos, NM, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e39c95265674fb</t>
+          <t>https://www.indeed.com/viewjob?jk=79bb920959efbb9a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Data Specialist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c0930580a5bcd07</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f0a26367981106</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Avantos AI</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, ETL, ELT, Docker</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48a21bba741abb42</t>
+          <t>https://www.indeed.com/viewjob?jk=728e979a13366d12</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Analyst Databricks</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hilton Grand Vacations</t>
+          <t>East Penn Manufacturing</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79bb920959efbb9a</t>
+          <t>https://www.indeed.com/viewjob?jk=75e660e8c44066de</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Specialist</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>East Penn Manufacturing</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f0a26367981106</t>
+          <t>https://www.indeed.com/viewjob?jk=def777e7298305bd</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Avantos AI</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728e979a13366d12</t>
+          <t>https://www.indeed.com/viewjob?jk=b818545ba973b739</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Irving, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b818545ba973b739</t>
+          <t>https://www.indeed.com/viewjob?jk=73033b8f87058bf3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - Big Data / AWS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73033b8f87058bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=8515f265503b068a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Software Engineer, Reconciliation &amp; Reporting</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>East Penn Manufacturing</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e660e8c44066de</t>
+          <t>https://www.indeed.com/viewjob?jk=9c826fbf927fd818</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>East Penn Manufacturing</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=def777e7298305bd</t>
+          <t>https://www.indeed.com/viewjob?jk=fd62b8e1edffefb2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Symple Lending</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, SQS, SNS, API Gateway, Scala, Kafka</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3dca5d46f438997</t>
+          <t>https://www.indeed.com/viewjob?jk=73c49ea64a65e4e4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data / AWS</t>
+          <t>Associate Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8515f265503b068a</t>
+          <t>https://www.indeed.com/viewjob?jk=8432eda41e25a208</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer, Reconciliation &amp; Reporting</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, Snowflake, ELT</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c826fbf927fd818</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff16008b78c40ca</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - GCP</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8432eda41e25a208</t>
+          <t>https://www.indeed.com/viewjob?jk=2c3f08d70fed55ec</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,54 +1896,54 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff16008b78c40ca</t>
+          <t>https://www.indeed.com/viewjob?jk=2c29f94189cd7da4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solution Architect, Sr</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala, Kafka, Cassandra</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c3f08d70fed55ec</t>
+          <t>https://www.indeed.com/viewjob?jk=fb30cf3f38d166f2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Technical Consultant - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1952,38 +1952,38 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c29f94189cd7da4</t>
+          <t>https://www.indeed.com/viewjob?jk=34f1952389da0adb</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Technical Consultant - Data &amp; Analytics</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>OrangePeople</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34f1952389da0adb</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4c6abe99182f2f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data &amp; Backend Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>OrangePeople</t>
+          <t>Chargie</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4c6abe99182f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=da930629a1994ea8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Backend Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Chargie</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da930629a1994ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=957b57fb2d35abb6</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Intellectyx</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, PostgreSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee6148be255d369</t>
+          <t>https://www.indeed.com/viewjob?jk=602b2be6bb9c1292</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Architect, Software Engineering</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Western Union</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8fc463b1f1234a3</t>
+          <t>https://www.indeed.com/viewjob?jk=66df8cc3622ab111</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f93d9150c8d68a7</t>
+          <t>https://www.indeed.com/viewjob?jk=eee6148be255d369</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d507f97d89d506</t>
+          <t>https://www.indeed.com/viewjob?jk=a8fc463b1f1234a3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed Software Engineer (FDE)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,104 +2271,104 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d38e42153f6fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=9f93d9150c8d68a7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>I O Engineer</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=882309c5e77e174d</t>
+          <t>https://www.indeed.com/viewjob?jk=74d507f97d89d506</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Senior Forward Deployed Software Engineer (FDE)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f7c2338fe900a7</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d38e42153f6fb0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>I O Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Purple Wave Auction</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, ETL, ELT, dbt</t>
+          <t>AWS, S3, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f455b3604d919def</t>
+          <t>https://www.indeed.com/viewjob?jk=882309c5e77e174d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Region 4 Education Service Center</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f972668b159bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=93f7c2338fe900a7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SEI Investments</t>
+          <t>Purple Wave Auction</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Snowflake, Oracle, SQL Server, MySQL, MongoDB, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d91881ede271802</t>
+          <t>https://www.indeed.com/viewjob?jk=f455b3604d919def</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Region 4 Education Service Center</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac2139dad458ba99</t>
+          <t>https://www.indeed.com/viewjob?jk=8f972668b159bfe1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Doggett Equipment Services Group</t>
+          <t>SEI Investments</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, IAM, Azure, Snowflake, Oracle, SQL Server, MySQL, MongoDB, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663cb751d821c5e4</t>
+          <t>https://www.indeed.com/viewjob?jk=3d91881ede271802</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Engineer III, DevOps</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70a210cdf39ed4c</t>
+          <t>https://www.indeed.com/viewjob?jk=ac2139dad458ba99</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS, Enterprise IAM</t>
+          <t>Forward Deployed Engineer - AI SOC</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eac59fd94e904980</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc6c1dd7963fdfd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - AI SOC</t>
+          <t>Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Doggett Equipment Services Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,104 +2621,104 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc6c1dd7963fdfd</t>
+          <t>https://www.indeed.com/viewjob?jk=663cb751d821c5e4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Software Engineer - Remote</t>
+          <t>Engineer III, DevOps</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=322a5edbf2a5360b</t>
+          <t>https://www.indeed.com/viewjob?jk=d70a210cdf39ed4c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Databricks Certified Data Engineer</t>
+          <t>Software Engineering SMTS, Enterprise IAM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba6921e4b5c7a034</t>
+          <t>https://www.indeed.com/viewjob?jk=eac59fd94e904980</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. IT Analyst</t>
+          <t>Senior Data Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, ETL, ELT, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfb5747a9d41a47e</t>
+          <t>https://www.indeed.com/viewjob?jk=322a5edbf2a5360b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cloud Engineer — multi-cloud (AWS &amp; Azure), infrastructure &amp; data services</t>
+          <t>Sr Databricks Certified Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NeevSys</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d9834a85f42798</t>
+          <t>https://www.indeed.com/viewjob?jk=ba6921e4b5c7a034</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. IT Analyst</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tebra</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Corona del Mar, CA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ELT, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, ETL, ELT, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55760e04a88682c7</t>
+          <t>https://www.indeed.com/viewjob?jk=dfb5747a9d41a47e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer 2- Kiewit Technology Group</t>
+          <t>Cloud Engineer — multi-cloud (AWS &amp; Azure), infrastructure &amp; data services</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>NeevSys</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e16ff09aa0b39352</t>
+          <t>https://www.indeed.com/viewjob?jk=61d9834a85f42798</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MGIC</t>
+          <t>Tebra</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>Corona del Mar, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40c5bedf068bb80</t>
+          <t>https://www.indeed.com/viewjob?jk=55760e04a88682c7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 2- Kiewit Technology Group</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TRIPLECOM</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>North Brunswick, NJ, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e6b5d69c186e13</t>
+          <t>https://www.indeed.com/viewjob?jk=e16ff09aa0b39352</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Embedded Product Analytics Senior Engineer</t>
+          <t>Senior Systems Engineer Analyst</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>MGIC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Mossville, IL, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01a1b2e1bcd66d65</t>
+          <t>https://www.indeed.com/viewjob?jk=c40c5bedf068bb80</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>TRIPLECOM</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>North Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=069422425deb2f92</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e6b5d69c186e13</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - QuantumBlack, AI by McKinsey</t>
+          <t>Principle Data &amp; IT Platform Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>OxyChem</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, NoSQL, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae2d8ccff2b67768</t>
+          <t>https://www.indeed.com/viewjob?jk=aafa6193d63da13a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I-II, Integration Platform Engineering</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbfe00edebebf90</t>
+          <t>https://www.indeed.com/viewjob?jk=069422425deb2f92</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, AI Services</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,17 +3076,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, ETL, MLOps</t>
+          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e6663fc1113d93</t>
+          <t>https://www.indeed.com/viewjob?jk=502f8e4e0f72f9d7</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=502f8e4e0f72f9d7</t>
+          <t>https://www.indeed.com/viewjob?jk=b6cd8290f0bbfe00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>Google Cloud Platform (GCP) Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>GLASSHOUSE SYSTEMS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6cd8290f0bbfe00</t>
+          <t>https://www.indeed.com/viewjob?jk=6caf875ac9a26f9e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Principle Data &amp; IT Platform Engineer</t>
+          <t>Senior Software Engineer - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>OxyChem</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, NoSQL, Power BI, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aafa6193d63da13a</t>
+          <t>https://www.indeed.com/viewjob?jk=ae2d8ccff2b67768</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Development Engineer – Python</t>
+          <t>Senior Software Engineer I-II, Integration Platform Engineering</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Cyient</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Champaign, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dc8bc961812dc0</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbfe00edebebf90</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Salesforce Development Engineer III</t>
+          <t>Senior AI Engineer, AI Services</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, ETL, MLOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e4b298a9510a69c</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e6663fc1113d93</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer II, Advanced Research (Remote)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nelnet</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44964b0a055385de</t>
+          <t>https://www.indeed.com/viewjob?jk=bae6de8914f99b9c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Linux Systems Engineer - Server Migration</t>
+          <t>Software Development Engineer – Python</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Cyient</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Champaign, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,94 +3331,94 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1c9201a8161c46</t>
+          <t>https://www.indeed.com/viewjob?jk=12dc8bc961812dc0</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Solovis</t>
+          <t>Nelnet</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, ETL, ELT, CI/CD, Docker, Kubernetes, AKS, Git</t>
+          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c802ebbce7a223a1</t>
+          <t>https://www.indeed.com/viewjob?jk=44964b0a055385de</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Linux Systems Engineer - Server Migration</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7a2187db3c65150</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1c9201a8161c46</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Software Engineer (Data)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Solovis</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Scala, PostgreSQL, ETL, ELT, CI/CD, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271ee7fda7a6bee4</t>
+          <t>https://www.indeed.com/viewjob?jk=c802ebbce7a223a1</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee5bdcb019976f9</t>
+          <t>https://www.indeed.com/viewjob?jk=d7a2187db3c65150</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae6cbdf5a874676</t>
+          <t>https://www.indeed.com/viewjob?jk=271ee7fda7a6bee4</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a7b2f239e82d02</t>
+          <t>https://www.indeed.com/viewjob?jk=dee5bdcb019976f9</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1b3b3f4ca0ce2d</t>
+          <t>https://www.indeed.com/viewjob?jk=eae6cbdf5a874676</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2153d438774a509a</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a7b2f239e82d02</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4985d9926908755</t>
+          <t>https://www.indeed.com/viewjob?jk=da1b3b3f4ca0ce2d</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8c4f97707d87774</t>
+          <t>https://www.indeed.com/viewjob?jk=2153d438774a509a</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f38308f7020f4ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=c4985d9926908755</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2848e822349e37</t>
+          <t>https://www.indeed.com/viewjob?jk=a8c4f97707d87774</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd7c699bcfc3b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=f38308f7020f4ab6</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31cc678d8a1b36d2</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2848e822349e37</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a81eae23fb3d49</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd7c699bcfc3b5b</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e650c829a90727ae</t>
+          <t>https://www.indeed.com/viewjob?jk=31cc678d8a1b36d2</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f80c3b16775bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a81eae23fb3d49</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7c9c591b425e81f</t>
+          <t>https://www.indeed.com/viewjob?jk=e650c829a90727ae</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2086bcd7f5b4a23</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f80c3b16775bd9</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a8bc962520011e7</t>
+          <t>https://www.indeed.com/viewjob?jk=d7c9c591b425e81f</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e29721616c97913</t>
+          <t>https://www.indeed.com/viewjob?jk=c2086bcd7f5b4a23</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0956fb4c5c9c0552</t>
+          <t>https://www.indeed.com/viewjob?jk=1a8bc962520011e7</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0691a1c6266d435b</t>
+          <t>https://www.indeed.com/viewjob?jk=6e29721616c97913</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a249a14145a4a4</t>
+          <t>https://www.indeed.com/viewjob?jk=0956fb4c5c9c0552</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70aa2099184a5196</t>
+          <t>https://www.indeed.com/viewjob?jk=0691a1c6266d435b</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059536b8aca9d2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a249a14145a4a4</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558ed485df852c51</t>
+          <t>https://www.indeed.com/viewjob?jk=70aa2099184a5196</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0e1e7cdd67ce1c</t>
+          <t>https://www.indeed.com/viewjob?jk=059536b8aca9d2a2</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7fb9b2593fe48de</t>
+          <t>https://www.indeed.com/viewjob?jk=558ed485df852c51</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f770060507dc86b</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0e1e7cdd67ce1c</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f1a4c01874e8f79</t>
+          <t>https://www.indeed.com/viewjob?jk=f7fb9b2593fe48de</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af904feccae24be9</t>
+          <t>https://www.indeed.com/viewjob?jk=4f770060507dc86b</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c4d3fcf499932c1</t>
+          <t>https://www.indeed.com/viewjob?jk=9f1a4c01874e8f79</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa87bd48c2643a2c</t>
+          <t>https://www.indeed.com/viewjob?jk=af904feccae24be9</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee0798b4cd7fde41</t>
+          <t>https://www.indeed.com/viewjob?jk=1c4d3fcf499932c1</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a59ae85c3362ed</t>
+          <t>https://www.indeed.com/viewjob?jk=fa87bd48c2643a2c</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e02fbdbb185ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=ee0798b4cd7fde41</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e53a0405898f435</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a59ae85c3362ed</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a18c489a6677b2</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e02fbdbb185ec1</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d36053a9cd0e254a</t>
+          <t>https://www.indeed.com/viewjob?jk=4e53a0405898f435</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc19476000a7ec6</t>
+          <t>https://www.indeed.com/viewjob?jk=b0a18c489a6677b2</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e4d40dfe7f3c0d8</t>
+          <t>https://www.indeed.com/viewjob?jk=d36053a9cd0e254a</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36bb93a99e60b085</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc19476000a7ec6</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43939234e151d703</t>
+          <t>https://www.indeed.com/viewjob?jk=5e4d40dfe7f3c0d8</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e67f673abfada57e</t>
+          <t>https://www.indeed.com/viewjob?jk=36bb93a99e60b085</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6c09cdff3fed03d</t>
+          <t>https://www.indeed.com/viewjob?jk=43939234e151d703</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0042baaea7e63584</t>
+          <t>https://www.indeed.com/viewjob?jk=e67f673abfada57e</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583da55552160f98</t>
+          <t>https://www.indeed.com/viewjob?jk=d6c09cdff3fed03d</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd52ee12f4c5cea</t>
+          <t>https://www.indeed.com/viewjob?jk=0042baaea7e63584</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d03eb01083cb07bd</t>
+          <t>https://www.indeed.com/viewjob?jk=583da55552160f98</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Pensacola, FL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, SQL Server, ETL, AKS</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d13a1873aa87c8</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd52ee12f4c5cea</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (NLP/LLM Focus)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Call Box</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, ETL, MLOps, MLflow, Terraform, Docker</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fea9b3e6393fbcc</t>
+          <t>https://www.indeed.com/viewjob?jk=d03eb01083cb07bd</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Transportation Data Scientist</t>
+          <t>Senior Machine Learning Engineer (NLP/LLM Focus)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>HNTB Corporation</t>
+          <t>Call Box</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
+          <t>AWS, Azure, GCP, Spark, Scala, ETL, MLOps, MLflow, Terraform, Docker</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62170821e4e69c98</t>
+          <t>https://www.indeed.com/viewjob?jk=6fea9b3e6393fbcc</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Transportation Data Scientist</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Argonne National Laboratory</t>
+          <t>HNTB Corporation</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Lemont, IL, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1699fa0e2d2c879d</t>
+          <t>https://www.indeed.com/viewjob?jk=62170821e4e69c98</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Public Trust Clearance Required</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Core-CSI LLC</t>
+          <t>Argonne National Laboratory</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Lemont, IL, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Polars, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df52133313b370b6</t>
+          <t>https://www.indeed.com/viewjob?jk=1699fa0e2d2c879d</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Senior Data Engineer - Public Trust Clearance Required</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Core-CSI LLC</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Polars, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4852036d2a4d2871</t>
+          <t>https://www.indeed.com/viewjob?jk=df52133313b370b6</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III-ETL/PySpark</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf6ee00929d1c54</t>
+          <t>https://www.indeed.com/viewjob?jk=4852036d2a4d2871</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e729f2a707e926b3</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf6ee00929d1c54</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Afficiency</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Vertex AI, Spark, Scala, Kafka, DynamoDB, Terraform, Docker</t>
+          <t>S3, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a16a037aab83b32</t>
+          <t>https://www.indeed.com/viewjob?jk=58359e4adc4e423e</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Risk Technology</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>STAAR Surgical</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lake Forest, CA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, Kafka, SQL Server, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, Oracle, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d2a8bd8e9419e9</t>
+          <t>https://www.indeed.com/viewjob?jk=1a6f9879069355ae</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Research Scientist II, Step 1-4</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>University of Alabama in Huntsville</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git, Python, SQL</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b876b59e168c817</t>
+          <t>https://www.indeed.com/viewjob?jk=3f88cd142184b0e3</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Sr Mgr, Software Engineering</t>
+          <t>Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Global KTech</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Power BI, Tableau, Airflow, Apache Airflow</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1779138f771f4150</t>
+          <t>https://www.indeed.com/viewjob?jk=1aab47487016cd9b</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineer</t>
+          <t>MuleSoft Integration Architect</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Global KTech</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aab47487016cd9b</t>
+          <t>https://www.indeed.com/viewjob?jk=da0dc7ca51d6016c</t>
         </is>
       </c>
     </row>
@@ -5566,29 +5566,29 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0dc7ca51d6016c</t>
+          <t>https://www.indeed.com/viewjob?jk=594a99f1fd9583f0</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>MuleSoft Integration Architect</t>
+          <t>Intermediate or Sr Software Developer (AI Platform &amp; Applications)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=594a99f1fd9583f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d1783e76eef53a01</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Intermediate or Sr Software Developer (AI Platform &amp; Applications)</t>
+          <t>DEXIS Sr. Full Stack Software Engineer, Cloud (Quakertown, PA)</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Envista Holdings</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Quakertown, PA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,34 +5631,34 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Cloud Storage, Scala, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1783e76eef53a01</t>
+          <t>https://www.indeed.com/viewjob?jk=2e7edc081f60cad1</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,34 +5666,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Kinesis, Azure, Vertex AI, Spark, Scala, Kafka, DynamoDB, Terraform, Docker</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=795435ece1bb17ca</t>
+          <t>https://www.indeed.com/viewjob?jk=1a16a037aab83b32</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Visual Edge IT</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Kubernetes, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e01c370f5d19ca30</t>
+          <t>https://www.indeed.com/viewjob?jk=abcdf98078942e6e</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Smart Apply Test Company</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,17 +5736,122 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfab7796442687c5</t>
+          <t>https://www.indeed.com/viewjob?jk=795435ece1bb17ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Senior Technical Architect</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>HCLTech</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Kubernetes, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e01c370f5d19ca30</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Risk Technology</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Millennium Management</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, S3, RDS, Scala, Kafka, SQL Server, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07d2a8bd8e9419e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer I- Operations</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Utah Valley University</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Oracle, SQL Server, MySQL, Splunk, CI/CD, CloudWatch, Azure Monitor, Python</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce8bc87fc76e47fd</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-28.xlsx
+++ b/results/job_matches_2026-07-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G155"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,60 +608,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Senior Integration Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>EDRAY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a43d246f182c799</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd9bc76eb207693</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75897b83126c3579</t>
+          <t>https://www.indeed.com/viewjob?jk=4e92864ad72da7b0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Data and Analytics Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EDRAY</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.8</v>
+        <v>19.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Azure</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd9bc76eb207693</t>
+          <t>https://www.indeed.com/viewjob?jk=6fca29e64567b9a7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Magpie Health Analytics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,46 +727,46 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SNS, RDS, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e92864ad72da7b0</t>
+          <t>https://www.indeed.com/viewjob?jk=81821640f49f76e3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data and Analytics Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fca29e64567b9a7</t>
+          <t>https://www.indeed.com/viewjob?jk=07a6d857864e2d3d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer- Veterans Affairs</t>
+          <t>Software Engineer Senior Consultant I -</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>THUNDERYARD SOLUTIONS</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,81 +797,81 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Cloud Storage</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b91074aae697c25</t>
+          <t>https://www.indeed.com/viewjob?jk=93914ebfffd3e0fa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Magpie Health Analytics</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SNS, RDS, Hadoop, Spark, PySpark</t>
+          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81821640f49f76e3</t>
+          <t>https://www.indeed.com/viewjob?jk=806ad6cc0b86fe80</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84fb98656d187561</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3d05891aeb413c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>AI Solutions Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, Splunk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=806ad6cc0b86fe80</t>
+          <t>https://www.indeed.com/viewjob?jk=5c685db79c3a032d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>Business Intelligence Data Modeler Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3d05891aeb413c</t>
+          <t>https://www.indeed.com/viewjob?jk=29badf7873509f1c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Solutions Architect</t>
+          <t>Site Reliability Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, Splunk</t>
+          <t>AWS, ECS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c685db79c3a032d</t>
+          <t>https://www.indeed.com/viewjob?jk=3789a24b75c1cfb1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Modeler Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29badf7873509f1c</t>
+          <t>https://www.indeed.com/viewjob?jk=5e3771f0c36b6f26</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e3771f0c36b6f26</t>
+          <t>https://www.indeed.com/viewjob?jk=a40f6ae7d2456a50</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40f6ae7d2456a50</t>
+          <t>https://www.indeed.com/viewjob?jk=51edf63fd9ce4d7a</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51edf63fd9ce4d7a</t>
+          <t>https://www.indeed.com/viewjob?jk=acd136a2c45725af</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Sr Software Engineer - AI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Lowe's Home Improvement</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd136a2c45725af</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1942c35e56392e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Hadoop+Spark(scala) Data Engineer</t>
+          <t>Software Engineer - AI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Virtues</t>
+          <t>Lowe's Home Improvement</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,29 +1186,29 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, HDFS, Hive, Sqoop, MapReduce</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aeb2bc3ba9b6d82</t>
+          <t>https://www.indeed.com/viewjob?jk=4b404e83cdfac818</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - AI</t>
+          <t>Data Engineer – Ab Initio &amp; GCP Modernization (contract)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lowe's Home Improvement</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1942c35e56392e</t>
+          <t>https://www.indeed.com/viewjob?jk=8a86e7ffe1b03ee9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer - AI</t>
+          <t>Senior MuleSoft Integration Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lowe's Home Improvement</t>
+          <t>VGMT GLOBAL IT SOLUTIONS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Goldsmith, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b404e83cdfac818</t>
+          <t>https://www.indeed.com/viewjob?jk=2b0fefd7a48d7cb0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Integration Developer</t>
+          <t>Azure Cloud Architect 4 (Remote)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>VGMT GLOBAL IT SOLUTIONS</t>
+          <t>Betis Group, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Goldsmith, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,42 +1301,42 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0fefd7a48d7cb0</t>
+          <t>https://www.indeed.com/viewjob?jk=61b88821804deb4d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Developer 3 (Full Stack Developer)</t>
+          <t>Sr Hadoop+Spark(scala) Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Edgewater Technical Associates</t>
+          <t>Virtues</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Los Alamos, NM, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e39c95265674fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8aeb2bc3ba9b6d82</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer, Reconciliation &amp; Reporting</t>
+          <t>Cloud/DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>CALIBRE Systems</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, Snowflake, ELT</t>
+          <t>Azure, Event Hubs, PostgreSQL, ETL, dbt, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c826fbf927fd818</t>
+          <t>https://www.indeed.com/viewjob?jk=23ea1dcc62a19705</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Reconciliation &amp; Reporting</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd62b8e1edffefb2</t>
+          <t>https://www.indeed.com/viewjob?jk=9c826fbf927fd818</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73c49ea64a65e4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=fd62b8e1edffefb2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - GCP</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8432eda41e25a208</t>
+          <t>https://www.indeed.com/viewjob?jk=73c49ea64a65e4e4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff16008b78c40ca</t>
+          <t>https://www.indeed.com/viewjob?jk=8432eda41e25a208</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Kinesis, API Gateway, IAM, RDS, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c3f08d70fed55ec</t>
+          <t>https://www.indeed.com/viewjob?jk=ceff5d9c8c0d8bc4</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Data Engineer, AQNav</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>SandboxAQ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Data Modeling, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b99b879200d82b7</t>
+          <t>https://www.indeed.com/viewjob?jk=7d054210a36a14a4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Intellectyx</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, PostgreSQL, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=602b2be6bb9c1292</t>
+          <t>https://www.indeed.com/viewjob?jk=8b99b879200d82b7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Architect, Software Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Western Union</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66df8cc3622ab111</t>
+          <t>https://www.indeed.com/viewjob?jk=21039e2b16d29978</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Architect, Software Engineering</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Western Union</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee6148be255d369</t>
+          <t>https://www.indeed.com/viewjob?jk=66df8cc3622ab111</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8fc463b1f1234a3</t>
+          <t>https://www.indeed.com/viewjob?jk=eee6148be255d369</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f93d9150c8d68a7</t>
+          <t>https://www.indeed.com/viewjob?jk=a8fc463b1f1234a3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d507f97d89d506</t>
+          <t>https://www.indeed.com/viewjob?jk=9f93d9150c8d68a7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed Software Engineer (FDE)</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Intellectyx</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,104 +2341,104 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, PostgreSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d38e42153f6fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=602b2be6bb9c1292</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>I O Engineer</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=882309c5e77e174d</t>
+          <t>https://www.indeed.com/viewjob?jk=74d507f97d89d506</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Senior Forward Deployed Software Engineer (FDE)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f7c2338fe900a7</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d38e42153f6fb0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>I O Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Purple Wave Auction</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, ETL, ELT, dbt</t>
+          <t>AWS, S3, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f455b3604d919def</t>
+          <t>https://www.indeed.com/viewjob?jk=882309c5e77e174d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Region 4 Education Service Center</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f972668b159bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=93f7c2338fe900a7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>VDH Cloud Data Engineer (Richmond)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SEI Investments</t>
+          <t>Betis Group, Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Snowflake, Oracle, SQL Server, MySQL, MongoDB, CI/CD, Maven</t>
+          <t>AWS, IAM, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d91881ede271802</t>
+          <t>https://www.indeed.com/viewjob?jk=04440d10b3bae1a9</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Purple Wave Auction</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hanover, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac2139dad458ba99</t>
+          <t>https://www.indeed.com/viewjob?jk=f455b3604d919def</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - AI SOC</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Region 4 Education Service Center</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc6c1dd7963fdfd</t>
+          <t>https://www.indeed.com/viewjob?jk=8f972668b159bfe1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Doggett Equipment Services Group</t>
+          <t>SEI Investments</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, IAM, Azure, Snowflake, Oracle, SQL Server, MySQL, MongoDB, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663cb751d821c5e4</t>
+          <t>https://www.indeed.com/viewjob?jk=3d91881ede271802</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Engineer III, DevOps</t>
+          <t>Forward Deployed Engineer - AI SOC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70a210cdf39ed4c</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc6c1dd7963fdfd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS, Enterprise IAM</t>
+          <t>Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Doggett Equipment Services Group</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,59 +2701,59 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eac59fd94e904980</t>
+          <t>https://www.indeed.com/viewjob?jk=663cb751d821c5e4</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Software Engineer - Remote</t>
+          <t>Engineer III, DevOps</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=322a5edbf2a5360b</t>
+          <t>https://www.indeed.com/viewjob?jk=d70a210cdf39ed4c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr Databricks Certified Data Engineer</t>
+          <t>Senior Data Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba6921e4b5c7a034</t>
+          <t>https://www.indeed.com/viewjob?jk=322a5edbf2a5360b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. IT Analyst</t>
+          <t>Sr Databricks Certified Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, ETL, ELT, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfb5747a9d41a47e</t>
+          <t>https://www.indeed.com/viewjob?jk=ba6921e4b5c7a034</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud Engineer — multi-cloud (AWS &amp; Azure), infrastructure &amp; data services</t>
+          <t>Sr. IT Analyst</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NeevSys</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, DynamoDB, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, ETL, ELT, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d9834a85f42798</t>
+          <t>https://www.indeed.com/viewjob?jk=dfb5747a9d41a47e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer — multi-cloud (AWS &amp; Azure), infrastructure &amp; data services</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tebra</t>
+          <t>NeevSys</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Corona del Mar, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ELT, MLOps, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55760e04a88682c7</t>
+          <t>https://www.indeed.com/viewjob?jk=61d9834a85f42798</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer 2- Kiewit Technology Group</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Tebra</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Corona del Mar, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e16ff09aa0b39352</t>
+          <t>https://www.indeed.com/viewjob?jk=55760e04a88682c7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer Analyst</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MGIC</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40c5bedf068bb80</t>
+          <t>https://www.indeed.com/viewjob?jk=069422425deb2f92</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TRIPLECOM</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>North Brunswick, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e6b5d69c186e13</t>
+          <t>https://www.indeed.com/viewjob?jk=502f8e4e0f72f9d7</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Principle Data &amp; IT Platform Engineer</t>
+          <t>Google Cloud Platform (GCP) Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>OxyChem</t>
+          <t>GLASSHOUSE SYSTEMS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, NoSQL, Power BI, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aafa6193d63da13a</t>
+          <t>https://www.indeed.com/viewjob?jk=6caf875ac9a26f9e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>Principle Data &amp; IT Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>OxyChem</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, NoSQL, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=069422425deb2f92</t>
+          <t>https://www.indeed.com/viewjob?jk=aafa6193d63da13a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>Senior AI Engineer, AI Services</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, ETL, MLOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=502f8e4e0f72f9d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e6663fc1113d93</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>Engineer II, Advanced Research (Remote)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6cd8290f0bbfe00</t>
+          <t>https://www.indeed.com/viewjob?jk=bae6de8914f99b9c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Google Cloud Platform (GCP) Architect</t>
+          <t>Software Development Engineer – Python</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GLASSHOUSE SYSTEMS</t>
+          <t>Cyient</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Lisle, IL, US USA</t>
+          <t>Champaign, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6caf875ac9a26f9e</t>
+          <t>https://www.indeed.com/viewjob?jk=12dc8bc961812dc0</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - QuantumBlack, AI by McKinsey</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Nelnet</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae2d8ccff2b67768</t>
+          <t>https://www.indeed.com/viewjob?jk=44964b0a055385de</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I-II, Integration Platform Engineering</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Oracle, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbfe00edebebf90</t>
+          <t>https://www.indeed.com/viewjob?jk=ed60b80bc0c985e3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, AI Services</t>
+          <t>Senior Software Engineer (Data)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Solovis</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, ETL, MLOps</t>
+          <t>AWS, Scala, PostgreSQL, ETL, ELT, CI/CD, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e6663fc1113d93</t>
+          <t>https://www.indeed.com/viewjob?jk=c802ebbce7a223a1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Engineer II, Advanced Research (Remote)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,129 +3296,129 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae6de8914f99b9c</t>
+          <t>https://www.indeed.com/viewjob?jk=d7a2187db3c65150</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Development Engineer – Python</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cyient</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Champaign, IL, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dc8bc961812dc0</t>
+          <t>https://www.indeed.com/viewjob?jk=271ee7fda7a6bee4</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Nelnet</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44964b0a055385de</t>
+          <t>https://www.indeed.com/viewjob?jk=dee5bdcb019976f9</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Linux Systems Engineer - Server Migration</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1c9201a8161c46</t>
+          <t>https://www.indeed.com/viewjob?jk=eae6cbdf5a874676</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Solovis</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, ETL, ELT, CI/CD, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c802ebbce7a223a1</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a7b2f239e82d02</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7a2187db3c65150</t>
+          <t>https://www.indeed.com/viewjob?jk=da1b3b3f4ca0ce2d</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271ee7fda7a6bee4</t>
+          <t>https://www.indeed.com/viewjob?jk=2153d438774a509a</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee5bdcb019976f9</t>
+          <t>https://www.indeed.com/viewjob?jk=c4985d9926908755</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae6cbdf5a874676</t>
+          <t>https://www.indeed.com/viewjob?jk=a8c4f97707d87774</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a7b2f239e82d02</t>
+          <t>https://www.indeed.com/viewjob?jk=f38308f7020f4ab6</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1b3b3f4ca0ce2d</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2848e822349e37</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2153d438774a509a</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd7c699bcfc3b5b</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4985d9926908755</t>
+          <t>https://www.indeed.com/viewjob?jk=31cc678d8a1b36d2</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8c4f97707d87774</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a81eae23fb3d49</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f38308f7020f4ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=e650c829a90727ae</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2848e822349e37</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f80c3b16775bd9</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd7c699bcfc3b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=d7c9c591b425e81f</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31cc678d8a1b36d2</t>
+          <t>https://www.indeed.com/viewjob?jk=c2086bcd7f5b4a23</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a81eae23fb3d49</t>
+          <t>https://www.indeed.com/viewjob?jk=1a8bc962520011e7</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e650c829a90727ae</t>
+          <t>https://www.indeed.com/viewjob?jk=6e29721616c97913</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f80c3b16775bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=0956fb4c5c9c0552</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7c9c591b425e81f</t>
+          <t>https://www.indeed.com/viewjob?jk=0691a1c6266d435b</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2086bcd7f5b4a23</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a249a14145a4a4</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a8bc962520011e7</t>
+          <t>https://www.indeed.com/viewjob?jk=70aa2099184a5196</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e29721616c97913</t>
+          <t>https://www.indeed.com/viewjob?jk=059536b8aca9d2a2</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0956fb4c5c9c0552</t>
+          <t>https://www.indeed.com/viewjob?jk=558ed485df852c51</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0691a1c6266d435b</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0e1e7cdd67ce1c</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a249a14145a4a4</t>
+          <t>https://www.indeed.com/viewjob?jk=f7fb9b2593fe48de</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70aa2099184a5196</t>
+          <t>https://www.indeed.com/viewjob?jk=4f770060507dc86b</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059536b8aca9d2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=9f1a4c01874e8f79</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558ed485df852c51</t>
+          <t>https://www.indeed.com/viewjob?jk=af904feccae24be9</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0e1e7cdd67ce1c</t>
+          <t>https://www.indeed.com/viewjob?jk=1c4d3fcf499932c1</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7fb9b2593fe48de</t>
+          <t>https://www.indeed.com/viewjob?jk=fa87bd48c2643a2c</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f770060507dc86b</t>
+          <t>https://www.indeed.com/viewjob?jk=ee0798b4cd7fde41</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f1a4c01874e8f79</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a59ae85c3362ed</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af904feccae24be9</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e02fbdbb185ec1</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c4d3fcf499932c1</t>
+          <t>https://www.indeed.com/viewjob?jk=4e53a0405898f435</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa87bd48c2643a2c</t>
+          <t>https://www.indeed.com/viewjob?jk=b0a18c489a6677b2</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee0798b4cd7fde41</t>
+          <t>https://www.indeed.com/viewjob?jk=d36053a9cd0e254a</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a59ae85c3362ed</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc19476000a7ec6</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e02fbdbb185ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=5e4d40dfe7f3c0d8</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e53a0405898f435</t>
+          <t>https://www.indeed.com/viewjob?jk=36bb93a99e60b085</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a18c489a6677b2</t>
+          <t>https://www.indeed.com/viewjob?jk=43939234e151d703</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d36053a9cd0e254a</t>
+          <t>https://www.indeed.com/viewjob?jk=e67f673abfada57e</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc19476000a7ec6</t>
+          <t>https://www.indeed.com/viewjob?jk=d6c09cdff3fed03d</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e4d40dfe7f3c0d8</t>
+          <t>https://www.indeed.com/viewjob?jk=0042baaea7e63584</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36bb93a99e60b085</t>
+          <t>https://www.indeed.com/viewjob?jk=583da55552160f98</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43939234e151d703</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd52ee12f4c5cea</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e67f673abfada57e</t>
+          <t>https://www.indeed.com/viewjob?jk=d03eb01083cb07bd</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Machine Learning Engineer (NLP/LLM Focus)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Call Box</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Spark, Scala, ETL, MLOps, MLflow, Terraform, Docker</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6c09cdff3fed03d</t>
+          <t>https://www.indeed.com/viewjob?jk=6fea9b3e6393fbcc</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Transportation Data Scientist</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>HNTB Corporation</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0042baaea7e63584</t>
+          <t>https://www.indeed.com/viewjob?jk=62170821e4e69c98</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer – Snowflake Data Ingestion &amp; Data Products (ECC Platform) - W2 Position</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>VTekis Consulting LLP</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583da55552160f98</t>
+          <t>https://www.indeed.com/viewjob?jk=6df590be06bde158</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Visual Edge IT</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd52ee12f4c5cea</t>
+          <t>https://www.indeed.com/viewjob?jk=abcdf98078942e6e</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Argonne National Laboratory</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Lemont, IL, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d03eb01083cb07bd</t>
+          <t>https://www.indeed.com/viewjob?jk=1699fa0e2d2c879d</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (NLP/LLM Focus)</t>
+          <t>Senior Data Engineer - Public Trust Clearance Required</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Call Box</t>
+          <t>Core-CSI LLC</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, ETL, MLOps, MLflow, Terraform, Docker</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Polars, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fea9b3e6393fbcc</t>
+          <t>https://www.indeed.com/viewjob?jk=df52133313b370b6</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Transportation Data Scientist</t>
+          <t>Software Engineer III-ETL/PySpark</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>HNTB Corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62170821e4e69c98</t>
+          <t>https://www.indeed.com/viewjob?jk=4852036d2a4d2871</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>DEXIS Sr. Full Stack Software Engineer, Cloud (Quakertown, PA)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Argonne National Laboratory</t>
+          <t>Envista Holdings</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Lemont, IL, US USA</t>
+          <t>Quakertown, PA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Cloud Storage, Scala, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1699fa0e2d2c879d</t>
+          <t>https://www.indeed.com/viewjob?jk=2e7edc081f60cad1</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Public Trust Clearance Required</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Core-CSI LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Polars, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df52133313b370b6</t>
+          <t>https://www.indeed.com/viewjob?jk=3f88cd142184b0e3</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Afficiency</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>S3, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4852036d2a4d2871</t>
+          <t>https://www.indeed.com/viewjob?jk=58359e4adc4e423e</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>STAAR Surgical</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Lake Forest, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Glue, Athena, IAM, RDS, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, Oracle, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf6ee00929d1c54</t>
+          <t>https://www.indeed.com/viewjob?jk=1a6f9879069355ae</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Afficiency</t>
+          <t>Global KTech</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58359e4adc4e423e</t>
+          <t>https://www.indeed.com/viewjob?jk=1aab47487016cd9b</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>MuleSoft Integration Architect</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>STAAR Surgical</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Lake Forest, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, Oracle, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a6f9879069355ae</t>
+          <t>https://www.indeed.com/viewjob?jk=da0dc7ca51d6016c</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>MuleSoft Integration Architect</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f88cd142184b0e3</t>
+          <t>https://www.indeed.com/viewjob?jk=594a99f1fd9583f0</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineer</t>
+          <t>Intermediate or Sr Software Developer (AI Platform &amp; Applications)</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Global KTech</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aab47487016cd9b</t>
+          <t>https://www.indeed.com/viewjob?jk=d1783e76eef53a01</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MuleSoft Integration Architect</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0dc7ca51d6016c</t>
+          <t>https://www.indeed.com/viewjob?jk=795435ece1bb17ca</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MuleSoft Integration Architect</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Kubernetes, SonarQube, Git</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,19 +5571,19 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=594a99f1fd9583f0</t>
+          <t>https://www.indeed.com/viewjob?jk=e01c370f5d19ca30</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Intermediate or Sr Software Developer (AI Platform &amp; Applications)</t>
+          <t>Site Reliability Engineer I- Operations</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Utah Valley University</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Oracle, SQL Server, MySQL, Splunk, CI/CD, CloudWatch, Azure Monitor, Python</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1783e76eef53a01</t>
+          <t>https://www.indeed.com/viewjob?jk=ce8bc87fc76e47fd</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>DEXIS Sr. Full Stack Software Engineer, Cloud (Quakertown, PA)</t>
+          <t>Senior Software Engineer - Risk Technology</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Envista Holdings</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Quakertown, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,227 +5631,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Cloud Storage, Scala, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Redshift, S3, RDS, Scala, Kafka, SQL Server, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e7edc081f60cad1</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Sr Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Azure, Vertex AI, Spark, Scala, Kafka, DynamoDB, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a16a037aab83b32</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Visual Edge IT</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, ELT, dbt, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=abcdf98078942e6e</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Full Stack Solutions Developer – Java</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=795435ece1bb17ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Senior Technical Architect</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>HCLTech</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Kubernetes, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e01c370f5d19ca30</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Risk Technology</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Millennium Management</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, RDS, Scala, Kafka, SQL Server, CI/CD, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=07d2a8bd8e9419e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer I- Operations</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Utah Valley University</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Oracle, SQL Server, MySQL, Splunk, CI/CD, CloudWatch, Azure Monitor, Python</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ce8bc87fc76e47fd</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-28.xlsx
+++ b/results/job_matches_2026-07-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G149"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,200 +573,200 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Integration Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>EDRAY</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e8b241f5073b73</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd9bc76eb207693</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EDRAY</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Azure</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd9bc76eb207693</t>
+          <t>https://www.indeed.com/viewjob?jk=4e92864ad72da7b0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data and Analytics Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e92864ad72da7b0</t>
+          <t>https://www.indeed.com/viewjob?jk=6fca29e64567b9a7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data and Analytics Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Magpie Health Analytics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SNS, RDS, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fca29e64567b9a7</t>
+          <t>https://www.indeed.com/viewjob?jk=81821640f49f76e3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Magpie Health Analytics</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SNS, RDS, Hadoop, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81821640f49f76e3</t>
+          <t>https://www.indeed.com/viewjob?jk=07a6d857864e2d3d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07a6d857864e2d3d</t>
+          <t>https://www.indeed.com/viewjob?jk=806ad6cc0b86fe80</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer Senior Consultant I -</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,38 +797,38 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93914ebfffd3e0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3d05891aeb413c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>SentiLink</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=806ad6cc0b86fe80</t>
+          <t>https://www.indeed.com/viewjob?jk=dc29164f164ed75f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>AI Solutions Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -867,108 +867,108 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, Splunk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3d05891aeb413c</t>
+          <t>https://www.indeed.com/viewjob?jk=5c685db79c3a032d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Solutions Architect</t>
+          <t>Business Intelligence Data Modeler Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, Splunk</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c685db79c3a032d</t>
+          <t>https://www.indeed.com/viewjob?jk=29badf7873509f1c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Modeler Engineer II</t>
+          <t>Site Reliability Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, ECS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29badf7873509f1c</t>
+          <t>https://www.indeed.com/viewjob?jk=3789a24b75c1cfb1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (Hybrid)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3789a24b75c1cfb1</t>
+          <t>https://www.indeed.com/viewjob?jk=cba2bebe1f3a11a0</t>
         </is>
       </c>
     </row>
@@ -1028,60 +1028,60 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Azure, GCP, Scala, PostgreSQL, DynamoDB, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40f6ae7d2456a50</t>
+          <t>https://www.indeed.com/viewjob?jk=89b591f23029748a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Data Engineer – Ab Initio &amp; GCP Modernization (contract)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,59 +1091,59 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51edf63fd9ce4d7a</t>
+          <t>https://www.indeed.com/viewjob?jk=8a86e7ffe1b03ee9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Azure Cloud Architect 4 (Remote)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Betis Group, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling</t>
+          <t>S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd136a2c45725af</t>
+          <t>https://www.indeed.com/viewjob?jk=61b88821804deb4d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - AI</t>
+          <t>Senior MuleSoft Integration Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lowe's Home Improvement</t>
+          <t>VGMT GLOBAL IT SOLUTIONS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Goldsmith, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,112 +1151,112 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1942c35e56392e</t>
+          <t>https://www.indeed.com/viewjob?jk=2b0fefd7a48d7cb0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer - AI</t>
+          <t>Sr Hadoop+Spark(scala) Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lowe's Home Improvement</t>
+          <t>Virtues</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Spark, PySpark, Scala, MLOps</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b404e83cdfac818</t>
+          <t>https://www.indeed.com/viewjob?jk=8aeb2bc3ba9b6d82</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer – Ab Initio &amp; GCP Modernization (contract)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a86e7ffe1b03ee9</t>
+          <t>https://www.indeed.com/viewjob?jk=48a21bba741abb42</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Integration Developer</t>
+          <t>Analyst Databricks</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>VGMT GLOBAL IT SOLUTIONS</t>
+          <t>Hilton Grand Vacations</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Goldsmith, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,59 +1266,59 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0fefd7a48d7cb0</t>
+          <t>https://www.indeed.com/viewjob?jk=79bb920959efbb9a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Azure Cloud Architect 4 (Remote)</t>
+          <t>Senior Data Specialist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Betis Group, Inc.</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61b88821804deb4d</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f0a26367981106</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Hadoop+Spark(scala) Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Virtues</t>
+          <t>Avantos AI</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aeb2bc3ba9b6d82</t>
+          <t>https://www.indeed.com/viewjob?jk=728e979a13366d12</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>East Penn Manufacturing</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, ETL, ELT, Docker</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48a21bba741abb42</t>
+          <t>https://www.indeed.com/viewjob?jk=75e660e8c44066de</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Analyst Databricks</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hilton Grand Vacations</t>
+          <t>East Penn Manufacturing</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79bb920959efbb9a</t>
+          <t>https://www.indeed.com/viewjob?jk=def777e7298305bd</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Specialist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f0a26367981106</t>
+          <t>https://www.indeed.com/viewjob?jk=b818545ba973b739</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Avantos AI</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728e979a13366d12</t>
+          <t>https://www.indeed.com/viewjob?jk=73033b8f87058bf3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Software Engineer III - Big Data / AWS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>East Penn Manufacturing</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,129 +1511,129 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e660e8c44066de</t>
+          <t>https://www.indeed.com/viewjob?jk=8515f265503b068a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Senior DevOps Engineer (EKS/Kubernetes)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>East Penn Manufacturing</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, IAM, RDS, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=def777e7298305bd</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2a2a8b73dd0dce</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer and Analyst</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BETTER WORLD BOOKS MARKETPLACE INC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irving, NY, US USA</t>
+          <t>Mishawaka, IN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b818545ba973b739</t>
+          <t>https://www.indeed.com/viewjob?jk=d84d40c0f777cc95</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud/DevOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CALIBRE Systems</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>Azure, Event Hubs, PostgreSQL, ETL, dbt, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73033b8f87058bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=23ea1dcc62a19705</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data / AWS</t>
+          <t>Software Engineer, Reconciliation &amp; Reporting</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, RDS, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8515f265503b068a</t>
+          <t>https://www.indeed.com/viewjob?jk=9c826fbf927fd818</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloud/DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CALIBRE Systems</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, PostgreSQL, ETL, dbt, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23ea1dcc62a19705</t>
+          <t>https://www.indeed.com/viewjob?jk=fd62b8e1edffefb2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer, Reconciliation &amp; Reporting</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, Snowflake, ELT</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c826fbf927fd818</t>
+          <t>https://www.indeed.com/viewjob?jk=73c49ea64a65e4e4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd62b8e1edffefb2</t>
+          <t>https://www.indeed.com/viewjob?jk=8432eda41e25a208</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,77 +1781,77 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, Kinesis, API Gateway, IAM, RDS, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73c49ea64a65e4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=ceff5d9c8c0d8bc4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - GCP</t>
+          <t>Solution Architect, Sr</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala, Kafka, Cassandra</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8432eda41e25a208</t>
+          <t>https://www.indeed.com/viewjob?jk=fb30cf3f38d166f2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Technical Consultant - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, API Gateway, IAM, RDS, Scala, Kafka, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,59 +1861,59 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceff5d9c8c0d8bc4</t>
+          <t>https://www.indeed.com/viewjob?jk=34f1952389da0adb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c29f94189cd7da4</t>
+          <t>https://www.indeed.com/viewjob?jk=957b57fb2d35abb6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Solution Architect, Sr</t>
+          <t>Data Engineer, AQNav</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>SandboxAQ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala, Kafka, Cassandra</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Data Modeling, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb30cf3f38d166f2</t>
+          <t>https://www.indeed.com/viewjob?jk=7d054210a36a14a4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Technical Consultant - Data &amp; Analytics</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Azure, Databricks, Cloud Storage, Hadoop, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34f1952389da0adb</t>
+          <t>https://www.indeed.com/viewjob?jk=8b99b879200d82b7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OrangePeople</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4c6abe99182f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=9acd7b6c90f890ed</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Backend Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Chargie</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, Data Modeling, ETL, Power BI</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da930629a1994ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e76f3094c53201</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=957b57fb2d35abb6</t>
+          <t>https://www.indeed.com/viewjob?jk=492012b7cd47b7f1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer, AQNav</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SandboxAQ</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Data Modeling, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d054210a36a14a4</t>
+          <t>https://www.indeed.com/viewjob?jk=21039e2b16d29978</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>Intellectyx</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, PostgreSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b99b879200d82b7</t>
+          <t>https://www.indeed.com/viewjob?jk=602b2be6bb9c1292</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Architect, Software Engineering</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AutoSavvy</t>
+          <t>Western Union</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Woods Cross, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21039e2b16d29978</t>
+          <t>https://www.indeed.com/viewjob?jk=66df8cc3622ab111</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Architect, Software Engineering</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Western Union</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66df8cc3622ab111</t>
+          <t>https://www.indeed.com/viewjob?jk=74d507f97d89d506</t>
         </is>
       </c>
     </row>
@@ -2323,25 +2323,25 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>I O Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Intellectyx</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, PostgreSQL, Power BI, Tableau</t>
+          <t>AWS, S3, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,94 +2351,94 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=602b2be6bb9c1292</t>
+          <t>https://www.indeed.com/viewjob?jk=882309c5e77e174d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d507f97d89d506</t>
+          <t>https://www.indeed.com/viewjob?jk=93f7c2338fe900a7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed Software Engineer (FDE)</t>
+          <t>VDH Cloud Data Engineer (Richmond)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Betis Group, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, IAM, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d38e42153f6fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=04440d10b3bae1a9</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>I O Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Purple Wave Auction</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=882309c5e77e174d</t>
+          <t>https://www.indeed.com/viewjob?jk=f455b3604d919def</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Region 4 Education Service Center</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f7c2338fe900a7</t>
+          <t>https://www.indeed.com/viewjob?jk=8f972668b159bfe1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>VDH Cloud Data Engineer (Richmond)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Betis Group, Inc.</t>
+          <t>SEI Investments</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Snowflake, Oracle, SQL Server, MySQL, MongoDB, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04440d10b3bae1a9</t>
+          <t>https://www.indeed.com/viewjob?jk=3d91881ede271802</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Purple Wave Auction</t>
+          <t>Doggett Equipment Services Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f455b3604d919def</t>
+          <t>https://www.indeed.com/viewjob?jk=663cb751d821c5e4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer III, DevOps</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Region 4 Education Service Center</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f972668b159bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=d70a210cdf39ed4c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Forward Deployed Engineer - AI SOC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SEI Investments</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Snowflake, Oracle, SQL Server, MySQL, MongoDB, CI/CD, Maven</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d91881ede271802</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc6c1dd7963fdfd</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - AI SOC</t>
+          <t>Senior Data Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,94 +2666,94 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc6c1dd7963fdfd</t>
+          <t>https://www.indeed.com/viewjob?jk=322a5edbf2a5360b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Sr. Software Engineer - Analytics Platform</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Doggett Equipment Services Group</t>
+          <t>Addepar</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD, Terraform, Datadog</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663cb751d821c5e4</t>
+          <t>https://www.indeed.com/viewjob?jk=a7bc12b85366baa5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Engineer III, DevOps</t>
+          <t>Sr Databricks Certified Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70a210cdf39ed4c</t>
+          <t>https://www.indeed.com/viewjob?jk=ba6921e4b5c7a034</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Software Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>RS21: A Data Science and Visualization Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=322a5edbf2a5360b</t>
+          <t>https://www.indeed.com/viewjob?jk=a873a920e8efc235</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Databricks Certified Data Engineer</t>
+          <t>Sr. IT Analyst</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, ETL, ELT, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba6921e4b5c7a034</t>
+          <t>https://www.indeed.com/viewjob?jk=dfb5747a9d41a47e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. IT Analyst</t>
+          <t>Cloud Engineer — multi-cloud (AWS &amp; Azure), infrastructure &amp; data services</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>NeevSys</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, ETL, ELT, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfb5747a9d41a47e</t>
+          <t>https://www.indeed.com/viewjob?jk=61d9834a85f42798</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud Engineer — multi-cloud (AWS &amp; Azure), infrastructure &amp; data services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NeevSys</t>
+          <t>Tebra</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Corona del Mar, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, DynamoDB, CI/CD, Terraform</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d9834a85f42798</t>
+          <t>https://www.indeed.com/viewjob?jk=55760e04a88682c7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tebra</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Corona del Mar, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ELT, MLOps, CI/CD</t>
+          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55760e04a88682c7</t>
+          <t>https://www.indeed.com/viewjob?jk=069422425deb2f92</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>Google Cloud Platform (GCP) Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>GLASSHOUSE SYSTEMS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=069422425deb2f92</t>
+          <t>https://www.indeed.com/viewjob?jk=6caf875ac9a26f9e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>Engineer II, Advanced Research (Remote)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=502f8e4e0f72f9d7</t>
+          <t>https://www.indeed.com/viewjob?jk=bae6de8914f99b9c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Google Cloud Platform (GCP) Architect</t>
+          <t>Senior AI Engineer, AI Services</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GLASSHOUSE SYSTEMS</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lisle, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,77 +3006,77 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, ETL, MLOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6caf875ac9a26f9e</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e6663fc1113d93</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Principle Data &amp; IT Platform Engineer</t>
+          <t>(USA) Senior, Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>OxyChem</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, NoSQL, Power BI, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aafa6193d63da13a</t>
+          <t>https://www.indeed.com/viewjob?jk=315bd0fc30ec0b9d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, AI Services</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Kafka, Snowflake, Oracle, ETL, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Oracle, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e6663fc1113d93</t>
+          <t>https://www.indeed.com/viewjob?jk=ed60b80bc0c985e3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Engineer II, Advanced Research (Remote)</t>
+          <t>Senior Software Engineer (Data)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Solovis</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Scala, PostgreSQL, ETL, ELT, CI/CD, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,94 +3121,94 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae6de8914f99b9c</t>
+          <t>https://www.indeed.com/viewjob?jk=c802ebbce7a223a1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Development Engineer – Python</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cyient</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Champaign, IL, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dc8bc961812dc0</t>
+          <t>https://www.indeed.com/viewjob?jk=d7a2187db3c65150</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nelnet</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling, dbt</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44964b0a055385de</t>
+          <t>https://www.indeed.com/viewjob?jk=271ee7fda7a6bee4</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Oracle, NoSQL, ETL</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed60b80bc0c985e3</t>
+          <t>https://www.indeed.com/viewjob?jk=dee5bdcb019976f9</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Solovis</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, ETL, ELT, CI/CD, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c802ebbce7a223a1</t>
+          <t>https://www.indeed.com/viewjob?jk=eae6cbdf5a874676</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7a2187db3c65150</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a7b2f239e82d02</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271ee7fda7a6bee4</t>
+          <t>https://www.indeed.com/viewjob?jk=da1b3b3f4ca0ce2d</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee5bdcb019976f9</t>
+          <t>https://www.indeed.com/viewjob?jk=2153d438774a509a</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae6cbdf5a874676</t>
+          <t>https://www.indeed.com/viewjob?jk=c4985d9926908755</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a7b2f239e82d02</t>
+          <t>https://www.indeed.com/viewjob?jk=a8c4f97707d87774</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1b3b3f4ca0ce2d</t>
+          <t>https://www.indeed.com/viewjob?jk=f38308f7020f4ab6</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2153d438774a509a</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2848e822349e37</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4985d9926908755</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd7c699bcfc3b5b</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8c4f97707d87774</t>
+          <t>https://www.indeed.com/viewjob?jk=31cc678d8a1b36d2</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f38308f7020f4ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a81eae23fb3d49</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2848e822349e37</t>
+          <t>https://www.indeed.com/viewjob?jk=e650c829a90727ae</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd7c699bcfc3b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f80c3b16775bd9</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31cc678d8a1b36d2</t>
+          <t>https://www.indeed.com/viewjob?jk=d7c9c591b425e81f</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a81eae23fb3d49</t>
+          <t>https://www.indeed.com/viewjob?jk=c2086bcd7f5b4a23</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e650c829a90727ae</t>
+          <t>https://www.indeed.com/viewjob?jk=1a8bc962520011e7</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f80c3b16775bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=6e29721616c97913</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7c9c591b425e81f</t>
+          <t>https://www.indeed.com/viewjob?jk=0956fb4c5c9c0552</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2086bcd7f5b4a23</t>
+          <t>https://www.indeed.com/viewjob?jk=0691a1c6266d435b</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a8bc962520011e7</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a249a14145a4a4</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e29721616c97913</t>
+          <t>https://www.indeed.com/viewjob?jk=70aa2099184a5196</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0956fb4c5c9c0552</t>
+          <t>https://www.indeed.com/viewjob?jk=059536b8aca9d2a2</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0691a1c6266d435b</t>
+          <t>https://www.indeed.com/viewjob?jk=558ed485df852c51</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a249a14145a4a4</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0e1e7cdd67ce1c</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70aa2099184a5196</t>
+          <t>https://www.indeed.com/viewjob?jk=f7fb9b2593fe48de</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059536b8aca9d2a2</t>
+          <t>https://www.indeed.com/viewjob?jk=4f770060507dc86b</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=558ed485df852c51</t>
+          <t>https://www.indeed.com/viewjob?jk=9f1a4c01874e8f79</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0e1e7cdd67ce1c</t>
+          <t>https://www.indeed.com/viewjob?jk=af904feccae24be9</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7fb9b2593fe48de</t>
+          <t>https://www.indeed.com/viewjob?jk=1c4d3fcf499932c1</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f770060507dc86b</t>
+          <t>https://www.indeed.com/viewjob?jk=fa87bd48c2643a2c</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f1a4c01874e8f79</t>
+          <t>https://www.indeed.com/viewjob?jk=ee0798b4cd7fde41</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af904feccae24be9</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a59ae85c3362ed</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c4d3fcf499932c1</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e02fbdbb185ec1</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa87bd48c2643a2c</t>
+          <t>https://www.indeed.com/viewjob?jk=4e53a0405898f435</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee0798b4cd7fde41</t>
+          <t>https://www.indeed.com/viewjob?jk=b0a18c489a6677b2</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a59ae85c3362ed</t>
+          <t>https://www.indeed.com/viewjob?jk=d36053a9cd0e254a</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e02fbdbb185ec1</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc19476000a7ec6</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e53a0405898f435</t>
+          <t>https://www.indeed.com/viewjob?jk=5e4d40dfe7f3c0d8</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a18c489a6677b2</t>
+          <t>https://www.indeed.com/viewjob?jk=36bb93a99e60b085</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d36053a9cd0e254a</t>
+          <t>https://www.indeed.com/viewjob?jk=43939234e151d703</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc19476000a7ec6</t>
+          <t>https://www.indeed.com/viewjob?jk=e67f673abfada57e</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e4d40dfe7f3c0d8</t>
+          <t>https://www.indeed.com/viewjob?jk=d6c09cdff3fed03d</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36bb93a99e60b085</t>
+          <t>https://www.indeed.com/viewjob?jk=0042baaea7e63584</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43939234e151d703</t>
+          <t>https://www.indeed.com/viewjob?jk=583da55552160f98</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e67f673abfada57e</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd52ee12f4c5cea</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6c09cdff3fed03d</t>
+          <t>https://www.indeed.com/viewjob?jk=d03eb01083cb07bd</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Machine Learning Engineer (NLP/LLM Focus)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Call Box</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Spark, Scala, ETL, MLOps, MLflow, Terraform, Docker</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0042baaea7e63584</t>
+          <t>https://www.indeed.com/viewjob?jk=6fea9b3e6393fbcc</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Transportation Data Scientist</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>HNTB Corporation</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583da55552160f98</t>
+          <t>https://www.indeed.com/viewjob?jk=62170821e4e69c98</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>IT America Inc</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>Azure, Databricks, Spark, PySpark, Snowflake, ELT, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd52ee12f4c5cea</t>
+          <t>https://www.indeed.com/viewjob?jk=84c35dbd43e40c6e</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer – Snowflake Data Ingestion &amp; Data Products (ECC Platform) - W2 Position</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>VTekis Consulting LLP</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, SNS, RDS, Azure, GCP, Kafka, Snowflake, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d03eb01083cb07bd</t>
+          <t>https://www.indeed.com/viewjob?jk=6df590be06bde158</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (NLP/LLM Focus)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Call Box</t>
+          <t>Visual Edge IT</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, ETL, MLOps, MLflow, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fea9b3e6393fbcc</t>
+          <t>https://www.indeed.com/viewjob?jk=abcdf98078942e6e</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Transportation Data Scientist</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>HNTB Corporation</t>
+          <t>Argonne National Laboratory</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Lemont, IL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62170821e4e69c98</t>
+          <t>https://www.indeed.com/viewjob?jk=1699fa0e2d2c879d</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Data Engineer – Snowflake Data Ingestion &amp; Data Products (ECC Platform) - W2 Position</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>VTekis Consulting LLP</t>
+          <t>Afficiency</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>S3, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6df590be06bde158</t>
+          <t>https://www.indeed.com/viewjob?jk=58359e4adc4e423e</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Visual Edge IT</t>
+          <t>STAAR Surgical</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lake Forest, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, Oracle, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abcdf98078942e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=1a6f9879069355ae</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Argonne National Laboratory</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Lemont, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1699fa0e2d2c879d</t>
+          <t>https://www.indeed.com/viewjob?jk=3f88cd142184b0e3</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Public Trust Clearance Required</t>
+          <t>Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Core-CSI LLC</t>
+          <t>Global KTech</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Polars, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df52133313b370b6</t>
+          <t>https://www.indeed.com/viewjob?jk=1aab47487016cd9b</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>DEXIS Sr. Full Stack Software Engineer, Cloud (Quakertown, PA)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Envista Holdings</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Quakertown, PA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>API Gateway, RDS, Azure, Blob Storage, Cloud Storage, Scala, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4852036d2a4d2871</t>
+          <t>https://www.indeed.com/viewjob?jk=2e7edc081f60cad1</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DEXIS Sr. Full Stack Software Engineer, Cloud (Quakertown, PA)</t>
+          <t>Intermediate or Sr Software Developer (AI Platform &amp; Applications)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Envista Holdings</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Quakertown, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,24 +5246,24 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Blob Storage, Cloud Storage, Scala, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e7edc081f60cad1</t>
+          <t>https://www.indeed.com/viewjob?jk=d1783e76eef53a01</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5286,29 +5286,29 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f88cd142184b0e3</t>
+          <t>https://www.indeed.com/viewjob?jk=795435ece1bb17ca</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Site Reliability Engineer I- Operations</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Afficiency</t>
+          <t>Utah Valley University</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Azure, Oracle, SQL Server, MySQL, Splunk, CI/CD, CloudWatch, Azure Monitor, Python</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58359e4adc4e423e</t>
+          <t>https://www.indeed.com/viewjob?jk=ce8bc87fc76e47fd</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Senior Build Engineer, CI/CD Efficiency</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>STAAR Surgical</t>
+          <t>1X</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Lake Forest, CA, US USA</t>
+          <t>San Carlos, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, Oracle, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,287 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a6f9879069355ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Forward Deployment Engineer</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Global KTech</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1aab47487016cd9b</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>MuleSoft Integration Architect</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Appex Innovation</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da0dc7ca51d6016c</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>MuleSoft Integration Architect</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Appex Innovation</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=594a99f1fd9583f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Intermediate or Sr Software Developer (AI Platform &amp; Applications)</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Dayforce</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d1783e76eef53a01</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Full Stack Solutions Developer – Java</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=795435ece1bb17ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Senior Technical Architect</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>HCLTech</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Terraform, Kubernetes, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e01c370f5d19ca30</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer I- Operations</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Utah Valley University</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Oracle, SQL Server, MySQL, Splunk, CI/CD, CloudWatch, Azure Monitor, Python</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ce8bc87fc76e47fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Risk Technology</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Millennium Management</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, RDS, Scala, Kafka, SQL Server, CI/CD, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=07d2a8bd8e9419e9</t>
+          <t>https://www.indeed.com/viewjob?jk=428a640cbb343011</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-28.xlsx
+++ b/results/job_matches_2026-07-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:G140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,95 +503,95 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Strategist - Partner</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.6</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Redshift, Step Functions, API Gateway, RDS, Azure, Databricks, GCP, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d09b36193d9c21c6</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3661ad61353f4f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Strategist - Partner</t>
+          <t>Senior Integration Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>EDRAY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Step Functions, API Gateway, RDS, Azure, Databricks, GCP, Vertex AI, Spark</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3661ad61353f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd9bc76eb207693</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Data and Analytics Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EDRAY</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.8</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Azure</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,19 +601,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd9bc76eb207693</t>
+          <t>https://www.indeed.com/viewjob?jk=6fca29e64567b9a7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Magpie Health Analytics</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,46 +622,46 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SNS, RDS, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e92864ad72da7b0</t>
+          <t>https://www.indeed.com/viewjob?jk=81821640f49f76e3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data and Analytics Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fca29e64567b9a7</t>
+          <t>https://www.indeed.com/viewjob?jk=07a6d857864e2d3d</t>
         </is>
       </c>
     </row>
@@ -683,55 +683,55 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Magpie Health Analytics</t>
+          <t>Beghou Consulting</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SNS, RDS, Hadoop, Spark, PySpark</t>
+          <t>AWS, Redshift, ECS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81821640f49f76e3</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f912a249dfd587</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07a6d857864e2d3d</t>
+          <t>https://www.indeed.com/viewjob?jk=806ad6cc0b86fe80</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>SentiLink</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, GCP, BigQuery, Dataflow, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=806ad6cc0b86fe80</t>
+          <t>https://www.indeed.com/viewjob?jk=dc29164f164ed75f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Hadoop</t>
+          <t>AI Solutions Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,81 +797,81 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, Splunk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed3d05891aeb413c</t>
+          <t>https://www.indeed.com/viewjob?jk=5c685db79c3a032d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Business Intelligence Data Modeler Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SentiLink</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, SQS, SNS, RDS, Azure, GCP</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc29164f164ed75f</t>
+          <t>https://www.indeed.com/viewjob?jk=29badf7873509f1c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, Splunk</t>
+          <t>RDS, Databricks, Snowflake, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,42 +881,42 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c685db79c3a032d</t>
+          <t>https://www.indeed.com/viewjob?jk=bde0531612b3e34f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Modeler Engineer II</t>
+          <t>Azure Data / Search Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, SQL Server, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29badf7873509f1c</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa50a1b1f574ddb</t>
         </is>
       </c>
     </row>
@@ -1028,25 +1028,25 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Analytics Consultant</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Scala, PostgreSQL, DynamoDB, dbt, MLOps, CI/CD</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Star Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89b591f23029748a</t>
+          <t>https://www.indeed.com/viewjob?jk=aeee6db7ce552c75</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer – Ab Initio &amp; GCP Modernization (contract)</t>
+          <t>Senior Analytics Consultant</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,50 +1073,50 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Oracle, Data Modeling, ETL</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Star Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a86e7ffe1b03ee9</t>
+          <t>https://www.indeed.com/viewjob?jk=d801aeb87ea34c90</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Azure Cloud Architect 4 (Remote)</t>
+          <t>Senior Analytics Consultant</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Betis Group, Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Star Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61b88821804deb4d</t>
+          <t>https://www.indeed.com/viewjob?jk=0d76c6857bcadff4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Integration Developer</t>
+          <t>Senior Analytics Consultant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VGMT GLOBAL IT SOLUTIONS</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Goldsmith, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Star Schema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0fefd7a48d7cb0</t>
+          <t>https://www.indeed.com/viewjob?jk=92bafff774d1dbc4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Hadoop+Spark(scala) Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Virtues</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase</t>
+          <t>AWS, Glue, Azure, GCP, Scala, PostgreSQL, DynamoDB, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aeb2bc3ba9b6d82</t>
+          <t>https://www.indeed.com/viewjob?jk=89b591f23029748a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer – Ab Initio &amp; GCP Modernization (contract)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, ETL, ELT, Docker</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48a21bba741abb42</t>
+          <t>https://www.indeed.com/viewjob?jk=8a86e7ffe1b03ee9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Analyst Databricks</t>
+          <t>Azure Cloud Architect 4 (Remote)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hilton Grand Vacations</t>
+          <t>Betis Group, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>S3, RDS, Azure, Data Factory, Event Hubs, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,59 +1266,59 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79bb920959efbb9a</t>
+          <t>https://www.indeed.com/viewjob?jk=61b88821804deb4d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Specialist</t>
+          <t>Senior MuleSoft Integration Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>VGMT GLOBAL IT SOLUTIONS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Goldsmith, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1f0a26367981106</t>
+          <t>https://www.indeed.com/viewjob?jk=2b0fefd7a48d7cb0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr Hadoop+Spark(scala) Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Avantos AI</t>
+          <t>Virtues</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Hadoop, HDFS, Hive, Sqoop, MapReduce, HBase</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=728e979a13366d12</t>
+          <t>https://www.indeed.com/viewjob?jk=8aeb2bc3ba9b6d82</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>East Penn Manufacturing</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e660e8c44066de</t>
+          <t>https://www.indeed.com/viewjob?jk=48a21bba741abb42</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>FinOps Engineer (contract)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>East Penn Manufacturing</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=def777e7298305bd</t>
+          <t>https://www.indeed.com/viewjob?jk=6fda2e305a92e01c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Analyst Databricks</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Hilton Grand Vacations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Irving, NY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b818545ba973b739</t>
+          <t>https://www.indeed.com/viewjob?jk=79bb920959efbb9a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Specialist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73033b8f87058bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=e1f0a26367981106</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data / AWS</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Avantos AI</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,94 +1511,94 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8515f265503b068a</t>
+          <t>https://www.indeed.com/viewjob?jk=728e979a13366d12</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (EKS/Kubernetes)</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>East Penn Manufacturing</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2a2a8b73dd0dce</t>
+          <t>https://www.indeed.com/viewjob?jk=75e660e8c44066de</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer and Analyst</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BETTER WORLD BOOKS MARKETPLACE INC</t>
+          <t>East Penn Manufacturing</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Mishawaka, IN, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d84d40c0f777cc95</t>
+          <t>https://www.indeed.com/viewjob?jk=def777e7298305bd</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud/DevOps Engineer</t>
+          <t>Software Engineer III - Big Data / AWS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CALIBRE Systems</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, PostgreSQL, ETL, dbt, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23ea1dcc62a19705</t>
+          <t>https://www.indeed.com/viewjob?jk=8515f265503b068a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer, Reconciliation &amp; Reporting</t>
+          <t>Senior DevOps Engineer (EKS/Kubernetes)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, S3, IAM, RDS, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c826fbf927fd818</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2a2a8b73dd0dce</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer and Analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>BETTER WORLD BOOKS MARKETPLACE INC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Mishawaka, IN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd62b8e1edffefb2</t>
+          <t>https://www.indeed.com/viewjob?jk=d84d40c0f777cc95</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud/DevOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>CALIBRE Systems</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>Azure, Event Hubs, PostgreSQL, ETL, dbt, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73c49ea64a65e4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=23ea1dcc62a19705</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - GCP</t>
+          <t>Software Engineer, Reconciliation &amp; Reporting</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, NoSQL</t>
+          <t>AWS, RDS, BigQuery, Hadoop, Spark, PySpark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8432eda41e25a208</t>
+          <t>https://www.indeed.com/viewjob?jk=9c826fbf927fd818</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b99b879200d82b7</t>
+          <t>https://www.indeed.com/viewjob?jk=9acd7b6c90f890ed</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9acd7b6c90f890ed</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e76f3094c53201</t>
         </is>
       </c>
     </row>
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e76f3094c53201</t>
+          <t>https://www.indeed.com/viewjob?jk=492012b7cd47b7f1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>Intellectyx</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, PostgreSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=492012b7cd47b7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=602b2be6bb9c1292</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Architect, Software Engineering</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AutoSavvy</t>
+          <t>Western Union</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Woods Cross, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21039e2b16d29978</t>
+          <t>https://www.indeed.com/viewjob?jk=66df8cc3622ab111</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Intellectyx</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, PostgreSQL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=602b2be6bb9c1292</t>
+          <t>https://www.indeed.com/viewjob?jk=21039e2b16d29978</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Architect, Software Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Western Union</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Docker</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66df8cc3622ab111</t>
+          <t>https://www.indeed.com/viewjob?jk=eee6148be255d369</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>project44</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d507f97d89d506</t>
+          <t>https://www.indeed.com/viewjob?jk=a8fc463b1f1234a3</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee6148be255d369</t>
+          <t>https://www.indeed.com/viewjob?jk=9f93d9150c8d68a7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>I O Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, S3, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8fc463b1f1234a3</t>
+          <t>https://www.indeed.com/viewjob?jk=882309c5e77e174d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f93d9150c8d68a7</t>
+          <t>https://www.indeed.com/viewjob?jk=93f7c2338fe900a7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>I O Engineer</t>
+          <t>VDH Cloud Data Engineer (Richmond)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Betis Group, Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=882309c5e77e174d</t>
+          <t>https://www.indeed.com/viewjob?jk=04440d10b3bae1a9</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Purple Wave Auction</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f7c2338fe900a7</t>
+          <t>https://www.indeed.com/viewjob?jk=f455b3604d919def</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>VDH Cloud Data Engineer (Richmond)</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Betis Group, Inc.</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04440d10b3bae1a9</t>
+          <t>https://www.indeed.com/viewjob?jk=cb266de132067a63</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Purple Wave Auction</t>
+          <t>SEI Investments</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,29 +2446,29 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, Snowflake, Oracle, SQL Server, MySQL, MongoDB, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f455b3604d919def</t>
+          <t>https://www.indeed.com/viewjob?jk=3d91881ede271802</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Region 4 Education Service Center</t>
+          <t>Doggett Equipment Services Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f972668b159bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=663cb751d821c5e4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Engineer III, DevOps</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SEI Investments</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Snowflake, Oracle, SQL Server, MySQL, MongoDB, CI/CD, Maven</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d91881ede271802</t>
+          <t>https://www.indeed.com/viewjob?jk=d70a210cdf39ed4c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Forward Deployed Engineer - AI SOC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Doggett Equipment Services Group</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,77 +2551,77 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663cb751d821c5e4</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc6c1dd7963fdfd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Engineer III, DevOps</t>
+          <t>Senior Data Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70a210cdf39ed4c</t>
+          <t>https://www.indeed.com/viewjob?jk=322a5edbf2a5360b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - AI SOC</t>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc6c1dd7963fdfd</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0063f4f570d6eb</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Software Engineer - Remote</t>
+          <t>Sr. Software Engineer - Analytics Platform</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Addepar</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD, Terraform, Datadog</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=322a5edbf2a5360b</t>
+          <t>https://www.indeed.com/viewjob?jk=a7bc12b85366baa5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Analytics Platform</t>
+          <t>Sr Databricks Certified Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Addepar</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD, Terraform, Datadog</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7bc12b85366baa5</t>
+          <t>https://www.indeed.com/viewjob?jk=ba6921e4b5c7a034</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Databricks Certified Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>RS21: A Data Science and Visualization Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba6921e4b5c7a034</t>
+          <t>https://www.indeed.com/viewjob?jk=a873a920e8efc235</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. IT Analyst</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RS21: A Data Science and Visualization Company</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, ETL, ELT, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a873a920e8efc235</t>
+          <t>https://www.indeed.com/viewjob?jk=dfb5747a9d41a47e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. IT Analyst</t>
+          <t>Cloud Engineer — multi-cloud (AWS &amp; Azure), infrastructure &amp; data services</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>NeevSys</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Delta Live Tables, Scala, ETL, ELT, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfb5747a9d41a47e</t>
+          <t>https://www.indeed.com/viewjob?jk=61d9834a85f42798</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud Engineer — multi-cloud (AWS &amp; Azure), infrastructure &amp; data services</t>
+          <t>Junior Security Automation Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NeevSys</t>
+          <t>Fidelity National Financial</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, DynamoDB, CI/CD, Terraform</t>
+          <t>RDS, Azure, Blob Storage, Scala, REST API integration, Docker, Kubernetes, AKS, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d9834a85f42798</t>
+          <t>https://www.indeed.com/viewjob?jk=38b62aab1e8febeb</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tebra</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Corona del Mar, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ELT, MLOps, CI/CD</t>
+          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55760e04a88682c7</t>
+          <t>https://www.indeed.com/viewjob?jk=069422425deb2f92</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior AI Machine Learning Engineer</t>
+          <t>Google Cloud Platform (GCP) Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>GLASSHOUSE SYSTEMS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, IAM, RDS, GCP, Cloud Storage, Vertex AI, Scala, CI/CD, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=069422425deb2f92</t>
+          <t>https://www.indeed.com/viewjob?jk=6caf875ac9a26f9e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Google Cloud Platform (GCP) Architect</t>
+          <t>Automation Python Developer with SQL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GLASSHOUSE SYSTEMS</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Lisle, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, ETL, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6caf875ac9a26f9e</t>
+          <t>https://www.indeed.com/viewjob?jk=ace6613f71b5a995</t>
         </is>
       </c>
     </row>
@@ -4878,17 +4878,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Transportation Data Scientist</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>HNTB Corporation</t>
+          <t>IT America Inc</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, ETL, Power BI, Tableau, Git, Python</t>
+          <t>Azure, Databricks, Spark, PySpark, Snowflake, ELT, CI/CD, GitHub Actions, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62170821e4e69c98</t>
+          <t>https://www.indeed.com/viewjob?jk=84c35dbd43e40c6e</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Engineer – Snowflake Data Ingestion &amp; Data Products (ECC Platform) - W2 Position</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>IT America Inc</t>
+          <t>VTekis Consulting LLP</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Snowflake, ELT, CI/CD, GitHub Actions, Azure DevOps, Git</t>
+          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c35dbd43e40c6e</t>
+          <t>https://www.indeed.com/viewjob?jk=6df590be06bde158</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Data Engineer – Snowflake Data Ingestion &amp; Data Products (ECC Platform) - W2 Position</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>VTekis Consulting LLP</t>
+          <t>Visual Edge IT</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6df590be06bde158</t>
+          <t>https://www.indeed.com/viewjob?jk=abcdf98078942e6e</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Visual Edge IT</t>
+          <t>Argonne National Laboratory</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lemont, IL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abcdf98078942e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=1699fa0e2d2c879d</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer - GDX Order Management</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Argonne National Laboratory</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Lemont, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Data Modeling, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1699fa0e2d2c879d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9aa69716ef18f63</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Afficiency</t>
+          <t>Lumeris</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Vertex AI, PostgreSQL, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58359e4adc4e423e</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4dc79d645f2ca8</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>STAAR Surgical</t>
+          <t>Afficiency</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Lake Forest, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, Oracle, CI/CD, Azure DevOps, Git</t>
+          <t>S3, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a6f9879069355ae</t>
+          <t>https://www.indeed.com/viewjob?jk=58359e4adc4e423e</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>STAAR Surgical</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lake Forest, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, Oracle, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,19 +5151,19 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f88cd142184b0e3</t>
+          <t>https://www.indeed.com/viewjob?jk=1a6f9879069355ae</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Global KTech</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aab47487016cd9b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f88cd142184b0e3</t>
         </is>
       </c>
     </row>
@@ -5228,17 +5228,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Intermediate or Sr Software Developer (AI Platform &amp; Applications)</t>
+          <t>Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Global KTech</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1783e76eef53a01</t>
+          <t>https://www.indeed.com/viewjob?jk=1aab47487016cd9b</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Intermediate or Sr Software Developer (AI Platform &amp; Applications)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=795435ece1bb17ca</t>
+          <t>https://www.indeed.com/viewjob?jk=d1783e76eef53a01</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer I- Operations</t>
+          <t>Senior Build Engineer, CI/CD Efficiency</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Utah Valley University</t>
+          <t>1X</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Carlos, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,50 +5316,15 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Azure, Oracle, SQL Server, MySQL, Splunk, CI/CD, CloudWatch, Azure Monitor, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ce8bc87fc76e47fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Senior Build Engineer, CI/CD Efficiency</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>1X</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>San Carlos, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=428a640cbb343011</t>
         </is>
